--- a/proposal/collaboration/collaboration_shaver.xlsx
+++ b/proposal/collaboration/collaboration_shaver.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10404"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dillo\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/misunmin/proj/genesis21b/proposal/collaboration/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2079FE3-492D-428D-B479-33567740F134}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01BEC5AF-56C6-154F-BBDD-0E89EAF84AEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6975" yWindow="4695" windowWidth="28800" windowHeight="15825" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5760" yWindow="4700" windowWidth="28800" windowHeight="15820" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="3" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="99">
   <si>
     <r>
       <rPr>
@@ -375,6 +375,9 @@
   </si>
   <si>
     <t>0000-0001-7216-7350</t>
+  </si>
+  <si>
+    <t>Min, Misun</t>
   </si>
 </sst>
 </file>
@@ -1002,8 +1005,17 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -1011,19 +1023,10 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1031,24 +1034,7 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="6">
     <dxf>
       <fill>
         <patternFill>
@@ -1377,18 +1363,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="128.7109375" customWidth="1"/>
+    <col min="1" max="1" width="128.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" ht="395" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A5" s="25"/>
     </row>
   </sheetData>
@@ -1400,55 +1386,55 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B83B436-6788-4C38-91CF-FD8F698B4202}">
   <dimension ref="A1:D27"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="22.7109375" customWidth="1"/>
+    <col min="1" max="2" width="22.6640625" customWidth="1"/>
     <col min="3" max="3" width="24" style="2" customWidth="1"/>
-    <col min="4" max="4" width="45.7109375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="45.6640625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="45" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="45"/>
-      <c r="C1" s="46" t="s">
+      <c r="C1" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="46"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D1" s="47"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="45" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="45"/>
-      <c r="C2" s="46" t="s">
+      <c r="C2" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="46"/>
-    </row>
-    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D2" s="47"/>
+    </row>
+    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="45" t="s">
         <v>5</v>
       </c>
       <c r="B3" s="45"/>
-      <c r="C3" s="46" t="s">
+      <c r="C3" s="47" t="s">
         <v>96</v>
       </c>
-      <c r="D3" s="46"/>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D3" s="47"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="45" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="45"/>
-      <c r="C4" s="53" t="s">
+      <c r="C4" s="46" t="s">
         <v>95</v>
       </c>
-      <c r="D4" s="46"/>
-    </row>
-    <row r="5" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D4" s="47"/>
+    </row>
+    <row r="5" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="43" t="s">
         <v>7</v>
       </c>
@@ -1456,7 +1442,7 @@
       <c r="C6" s="39"/>
       <c r="D6" s="40"/>
     </row>
-    <row r="7" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="28" t="s">
         <v>8</v>
       </c>
@@ -1470,7 +1456,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="29" t="s">
         <v>51</v>
       </c>
@@ -1484,115 +1470,115 @@
         <v>94</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="33"/>
       <c r="B9" s="26"/>
       <c r="C9" s="27"/>
       <c r="D9" s="32"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="33"/>
       <c r="B10" s="26"/>
       <c r="C10" s="27"/>
       <c r="D10" s="34"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="33"/>
       <c r="B11" s="26"/>
       <c r="C11" s="27"/>
       <c r="D11" s="34"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="33"/>
       <c r="B12" s="26"/>
       <c r="C12" s="27"/>
       <c r="D12" s="34"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="33"/>
       <c r="B13" s="26"/>
       <c r="C13" s="27"/>
       <c r="D13" s="34"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="33"/>
       <c r="B14" s="26"/>
       <c r="C14" s="27"/>
       <c r="D14" s="34"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="33"/>
       <c r="B15" s="26"/>
       <c r="C15" s="27"/>
       <c r="D15" s="34"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="33"/>
       <c r="B16" s="26"/>
       <c r="C16" s="27"/>
       <c r="D16" s="34"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" s="33"/>
       <c r="B17" s="26"/>
       <c r="C17" s="27"/>
       <c r="D17" s="34"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" s="33"/>
       <c r="B18" s="26"/>
       <c r="C18" s="27"/>
       <c r="D18" s="34"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" s="33"/>
       <c r="B19" s="26"/>
       <c r="C19" s="27"/>
       <c r="D19" s="34"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" s="33"/>
       <c r="B20" s="26"/>
       <c r="C20" s="27"/>
       <c r="D20" s="34"/>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" s="33"/>
       <c r="B21" s="26"/>
       <c r="C21" s="27"/>
       <c r="D21" s="34"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" s="33"/>
       <c r="B22" s="26"/>
       <c r="C22" s="27"/>
       <c r="D22" s="34"/>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" s="33"/>
       <c r="B23" s="26"/>
       <c r="C23" s="27"/>
       <c r="D23" s="34"/>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" s="33"/>
       <c r="B24" s="26"/>
       <c r="C24" s="27"/>
       <c r="D24" s="34"/>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" s="33"/>
       <c r="B25" s="26"/>
       <c r="C25" s="27"/>
       <c r="D25" s="34"/>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" s="33"/>
       <c r="B26" s="26"/>
       <c r="C26" s="27"/>
       <c r="D26" s="34"/>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" s="33"/>
       <c r="B27" s="26"/>
       <c r="C27" s="27"/>
@@ -1611,7 +1597,7 @@
     <mergeCell ref="C3:D3"/>
   </mergeCells>
   <conditionalFormatting sqref="A8:D27">
-    <cfRule type="expression" dxfId="7" priority="2">
+    <cfRule type="expression" dxfId="5" priority="2">
       <formula>MOD(ROW()-1,2)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1629,77 +1615,77 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H411"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="22.7109375" customWidth="1"/>
-    <col min="3" max="4" width="22.7109375" style="2" customWidth="1"/>
-    <col min="5" max="5" width="25.140625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="45.7109375" style="2" customWidth="1"/>
-    <col min="7" max="7" width="35.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.42578125" customWidth="1"/>
+    <col min="1" max="2" width="22.6640625" customWidth="1"/>
+    <col min="3" max="4" width="22.6640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="25.1640625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="45.6640625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="35.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="45" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="45"/>
-      <c r="C1" s="46" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="46"/>
+      <c r="C1" s="47" t="s">
+        <v>94</v>
+      </c>
+      <c r="D1" s="47"/>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="45" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="45"/>
-      <c r="C2" s="46" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" s="46"/>
+      <c r="C2" s="47" t="s">
+        <v>98</v>
+      </c>
+      <c r="D2" s="47"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="45" t="s">
         <v>5</v>
       </c>
       <c r="B3" s="45"/>
-      <c r="C3" s="46" t="s">
+      <c r="C3" s="47" t="s">
         <v>96</v>
       </c>
-      <c r="D3" s="46"/>
+      <c r="D3" s="47"/>
       <c r="E3" s="3"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="45" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="45"/>
-      <c r="C4" s="53" t="s">
+      <c r="C4" s="46" t="s">
         <v>95</v>
       </c>
-      <c r="D4" s="46"/>
+      <c r="D4" s="47"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="49" t="s">
+    <row r="5" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="48" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="50"/>
-      <c r="C6" s="47" t="str">
+      <c r="B6" s="49"/>
+      <c r="C6" s="50" t="str">
         <f>"Collaborator Table - "&amp;C1&amp;" ("&amp;C2&amp;")"</f>
-        <v>Collaborator Table - Institution Name (Last (Family) Name, First (Given) Name)</v>
-      </c>
-      <c r="D6" s="47"/>
-      <c r="E6" s="47"/>
-      <c r="F6" s="47"/>
-      <c r="G6" s="47"/>
-      <c r="H6" s="48"/>
-    </row>
-    <row r="7" spans="1:8" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>Collaborator Table - Argonne National Laboratory (Min, Misun)</v>
+      </c>
+      <c r="D6" s="50"/>
+      <c r="E6" s="50"/>
+      <c r="F6" s="50"/>
+      <c r="G6" s="50"/>
+      <c r="H6" s="51"/>
+    </row>
+    <row r="7" spans="1:8" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="20" t="s">
         <v>8</v>
       </c>
@@ -1725,7 +1711,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A8" s="14" t="s">
         <v>51</v>
       </c>
@@ -1749,7 +1735,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="14" t="s">
         <v>51</v>
       </c>
@@ -1773,7 +1759,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="14" t="s">
         <v>51</v>
       </c>
@@ -1797,7 +1783,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="14" t="s">
         <v>51</v>
       </c>
@@ -1821,7 +1807,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="14" t="s">
         <v>51</v>
       </c>
@@ -1845,7 +1831,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="14" t="s">
         <v>51</v>
       </c>
@@ -1869,7 +1855,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="14" t="s">
         <v>51</v>
       </c>
@@ -1893,7 +1879,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="14" t="s">
         <v>51</v>
       </c>
@@ -1917,7 +1903,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="14" t="s">
         <v>51</v>
       </c>
@@ -1941,7 +1927,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="14" t="s">
         <v>51</v>
       </c>
@@ -1965,7 +1951,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="14" t="s">
         <v>51</v>
       </c>
@@ -1989,7 +1975,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="14" t="s">
         <v>51</v>
       </c>
@@ -2013,7 +1999,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="14" t="s">
         <v>51</v>
       </c>
@@ -2037,7 +2023,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="14" t="s">
         <v>51</v>
       </c>
@@ -2061,7 +2047,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" s="14" t="s">
         <v>51</v>
       </c>
@@ -2085,7 +2071,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="14" t="s">
         <v>51</v>
       </c>
@@ -2109,7 +2095,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
         <v>51</v>
       </c>
@@ -2133,7 +2119,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="4"/>
       <c r="B25" s="5"/>
       <c r="C25" s="42"/>
@@ -2143,7 +2129,7 @@
       <c r="G25" s="6"/>
       <c r="H25" s="7"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" s="4"/>
       <c r="B26" s="5"/>
       <c r="C26" s="42"/>
@@ -2153,7 +2139,7 @@
       <c r="G26" s="6"/>
       <c r="H26" s="7"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" s="4"/>
       <c r="B27" s="5"/>
       <c r="C27" s="42"/>
@@ -2163,7 +2149,7 @@
       <c r="G27" s="6"/>
       <c r="H27" s="7"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="4"/>
       <c r="B28" s="5"/>
       <c r="C28" s="42"/>
@@ -2173,7 +2159,7 @@
       <c r="G28" s="6"/>
       <c r="H28" s="7"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="4"/>
       <c r="B29" s="5"/>
       <c r="C29" s="42"/>
@@ -2183,7 +2169,7 @@
       <c r="G29" s="6"/>
       <c r="H29" s="7"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="4"/>
       <c r="B30" s="5"/>
       <c r="C30" s="42"/>
@@ -2193,7 +2179,7 @@
       <c r="G30" s="6"/>
       <c r="H30" s="7"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="4"/>
       <c r="B31" s="5"/>
       <c r="C31" s="42"/>
@@ -2203,7 +2189,7 @@
       <c r="G31" s="6"/>
       <c r="H31" s="7"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" s="4"/>
       <c r="B32" s="5"/>
       <c r="C32" s="42"/>
@@ -2213,7 +2199,7 @@
       <c r="G32" s="6"/>
       <c r="H32" s="7"/>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" s="4"/>
       <c r="B33" s="5"/>
       <c r="C33" s="42"/>
@@ -2223,7 +2209,7 @@
       <c r="G33" s="6"/>
       <c r="H33" s="7"/>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" s="4"/>
       <c r="B34" s="5"/>
       <c r="C34" s="42"/>
@@ -2233,7 +2219,7 @@
       <c r="G34" s="6"/>
       <c r="H34" s="7"/>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" s="4"/>
       <c r="B35" s="5"/>
       <c r="C35" s="42"/>
@@ -2243,7 +2229,7 @@
       <c r="G35" s="6"/>
       <c r="H35" s="7"/>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" s="4"/>
       <c r="B36" s="5"/>
       <c r="C36" s="42"/>
@@ -2253,7 +2239,7 @@
       <c r="G36" s="6"/>
       <c r="H36" s="7"/>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" s="4"/>
       <c r="B37" s="5"/>
       <c r="C37" s="42"/>
@@ -2263,7 +2249,7 @@
       <c r="G37" s="6"/>
       <c r="H37" s="7"/>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" s="4"/>
       <c r="B38" s="5"/>
       <c r="C38" s="42"/>
@@ -2273,7 +2259,7 @@
       <c r="G38" s="6"/>
       <c r="H38" s="7"/>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" s="4"/>
       <c r="B39" s="5"/>
       <c r="C39" s="42"/>
@@ -2283,7 +2269,7 @@
       <c r="G39" s="6"/>
       <c r="H39" s="7"/>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" s="4"/>
       <c r="B40" s="5"/>
       <c r="C40" s="42"/>
@@ -2293,7 +2279,7 @@
       <c r="G40" s="6"/>
       <c r="H40" s="7"/>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" s="4"/>
       <c r="B41" s="5"/>
       <c r="C41" s="42"/>
@@ -2303,7 +2289,7 @@
       <c r="G41" s="6"/>
       <c r="H41" s="7"/>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" s="4"/>
       <c r="B42" s="5"/>
       <c r="C42" s="42"/>
@@ -2313,7 +2299,7 @@
       <c r="G42" s="6"/>
       <c r="H42" s="7"/>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" s="4"/>
       <c r="B43" s="5"/>
       <c r="C43" s="42"/>
@@ -2323,7 +2309,7 @@
       <c r="G43" s="6"/>
       <c r="H43" s="7"/>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" s="4"/>
       <c r="B44" s="5"/>
       <c r="C44" s="42"/>
@@ -2333,7 +2319,7 @@
       <c r="G44" s="6"/>
       <c r="H44" s="7"/>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" s="4"/>
       <c r="B45" s="5"/>
       <c r="C45" s="42"/>
@@ -2343,7 +2329,7 @@
       <c r="G45" s="6"/>
       <c r="H45" s="7"/>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" s="4"/>
       <c r="B46" s="5"/>
       <c r="C46" s="42"/>
@@ -2353,7 +2339,7 @@
       <c r="G46" s="6"/>
       <c r="H46" s="7"/>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" s="4"/>
       <c r="B47" s="5"/>
       <c r="C47" s="42"/>
@@ -2363,7 +2349,7 @@
       <c r="G47" s="6"/>
       <c r="H47" s="7"/>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" s="4"/>
       <c r="B48" s="5"/>
       <c r="C48" s="42"/>
@@ -2373,7 +2359,7 @@
       <c r="G48" s="6"/>
       <c r="H48" s="7"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" s="4"/>
       <c r="B49" s="5"/>
       <c r="C49" s="42"/>
@@ -2383,7 +2369,7 @@
       <c r="G49" s="6"/>
       <c r="H49" s="7"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" s="4"/>
       <c r="B50" s="5"/>
       <c r="C50" s="42"/>
@@ -2393,7 +2379,7 @@
       <c r="G50" s="6"/>
       <c r="H50" s="7"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" s="4"/>
       <c r="B51" s="5"/>
       <c r="C51" s="42"/>
@@ -2403,7 +2389,7 @@
       <c r="G51" s="6"/>
       <c r="H51" s="7"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" s="4"/>
       <c r="B52" s="5"/>
       <c r="C52" s="42"/>
@@ -2413,7 +2399,7 @@
       <c r="G52" s="6"/>
       <c r="H52" s="7"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53" s="4"/>
       <c r="B53" s="5"/>
       <c r="C53" s="42"/>
@@ -2423,7 +2409,7 @@
       <c r="G53" s="6"/>
       <c r="H53" s="7"/>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54" s="4"/>
       <c r="B54" s="5"/>
       <c r="C54" s="42"/>
@@ -2433,7 +2419,7 @@
       <c r="G54" s="6"/>
       <c r="H54" s="7"/>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A55" s="4"/>
       <c r="B55" s="5"/>
       <c r="C55" s="42"/>
@@ -2443,7 +2429,7 @@
       <c r="G55" s="6"/>
       <c r="H55" s="7"/>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A56" s="4"/>
       <c r="B56" s="5"/>
       <c r="C56" s="42"/>
@@ -2453,7 +2439,7 @@
       <c r="G56" s="6"/>
       <c r="H56" s="7"/>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A57" s="4"/>
       <c r="B57" s="5"/>
       <c r="C57" s="42"/>
@@ -2463,7 +2449,7 @@
       <c r="G57" s="6"/>
       <c r="H57" s="7"/>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A58" s="4"/>
       <c r="B58" s="5"/>
       <c r="C58" s="42"/>
@@ -2473,7 +2459,7 @@
       <c r="G58" s="6"/>
       <c r="H58" s="7"/>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A59" s="4"/>
       <c r="B59" s="5"/>
       <c r="C59" s="42"/>
@@ -2483,7 +2469,7 @@
       <c r="G59" s="6"/>
       <c r="H59" s="7"/>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A60" s="4"/>
       <c r="B60" s="5"/>
       <c r="C60" s="42"/>
@@ -2493,7 +2479,7 @@
       <c r="G60" s="6"/>
       <c r="H60" s="7"/>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A61" s="4"/>
       <c r="B61" s="5"/>
       <c r="C61" s="42"/>
@@ -2503,7 +2489,7 @@
       <c r="G61" s="6"/>
       <c r="H61" s="7"/>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A62" s="4"/>
       <c r="B62" s="5"/>
       <c r="C62" s="42"/>
@@ -2513,7 +2499,7 @@
       <c r="G62" s="6"/>
       <c r="H62" s="7"/>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A63" s="4"/>
       <c r="B63" s="5"/>
       <c r="C63" s="42"/>
@@ -2523,7 +2509,7 @@
       <c r="G63" s="6"/>
       <c r="H63" s="7"/>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A64" s="4"/>
       <c r="B64" s="5"/>
       <c r="C64" s="42"/>
@@ -2533,7 +2519,7 @@
       <c r="G64" s="6"/>
       <c r="H64" s="7"/>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A65" s="4"/>
       <c r="B65" s="5"/>
       <c r="C65" s="42"/>
@@ -2543,7 +2529,7 @@
       <c r="G65" s="6"/>
       <c r="H65" s="7"/>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A66" s="4"/>
       <c r="B66" s="5"/>
       <c r="C66" s="42"/>
@@ -2553,7 +2539,7 @@
       <c r="G66" s="6"/>
       <c r="H66" s="7"/>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A67" s="4"/>
       <c r="B67" s="5"/>
       <c r="C67" s="42"/>
@@ -2563,7 +2549,7 @@
       <c r="G67" s="6"/>
       <c r="H67" s="7"/>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A68" s="4"/>
       <c r="B68" s="5"/>
       <c r="C68" s="42"/>
@@ -2573,7 +2559,7 @@
       <c r="G68" s="6"/>
       <c r="H68" s="7"/>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A69" s="4"/>
       <c r="B69" s="5"/>
       <c r="C69" s="42"/>
@@ -2583,7 +2569,7 @@
       <c r="G69" s="6"/>
       <c r="H69" s="7"/>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A70" s="4"/>
       <c r="B70" s="5"/>
       <c r="C70" s="42"/>
@@ -2593,7 +2579,7 @@
       <c r="G70" s="6"/>
       <c r="H70" s="7"/>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A71" s="4"/>
       <c r="B71" s="5"/>
       <c r="C71" s="42"/>
@@ -2603,7 +2589,7 @@
       <c r="G71" s="6"/>
       <c r="H71" s="7"/>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A72" s="4"/>
       <c r="B72" s="5"/>
       <c r="C72" s="42"/>
@@ -2613,7 +2599,7 @@
       <c r="G72" s="6"/>
       <c r="H72" s="7"/>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A73" s="4"/>
       <c r="B73" s="5"/>
       <c r="C73" s="42"/>
@@ -2623,7 +2609,7 @@
       <c r="G73" s="6"/>
       <c r="H73" s="7"/>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A74" s="4"/>
       <c r="B74" s="5"/>
       <c r="C74" s="42"/>
@@ -2633,7 +2619,7 @@
       <c r="G74" s="6"/>
       <c r="H74" s="7"/>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A75" s="4"/>
       <c r="B75" s="5"/>
       <c r="C75" s="42"/>
@@ -2643,7 +2629,7 @@
       <c r="G75" s="6"/>
       <c r="H75" s="7"/>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A76" s="4"/>
       <c r="B76" s="5"/>
       <c r="C76" s="42"/>
@@ -2653,7 +2639,7 @@
       <c r="G76" s="6"/>
       <c r="H76" s="7"/>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A77" s="4"/>
       <c r="B77" s="5"/>
       <c r="C77" s="42"/>
@@ -2663,7 +2649,7 @@
       <c r="G77" s="6"/>
       <c r="H77" s="7"/>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A78" s="4"/>
       <c r="B78" s="5"/>
       <c r="C78" s="42"/>
@@ -2673,7 +2659,7 @@
       <c r="G78" s="6"/>
       <c r="H78" s="7"/>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A79" s="4"/>
       <c r="B79" s="5"/>
       <c r="C79" s="42"/>
@@ -2683,7 +2669,7 @@
       <c r="G79" s="6"/>
       <c r="H79" s="7"/>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A80" s="4"/>
       <c r="B80" s="5"/>
       <c r="C80" s="42"/>
@@ -2693,7 +2679,7 @@
       <c r="G80" s="6"/>
       <c r="H80" s="7"/>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A81" s="4"/>
       <c r="B81" s="5"/>
       <c r="C81" s="42"/>
@@ -2703,7 +2689,7 @@
       <c r="G81" s="6"/>
       <c r="H81" s="7"/>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A82" s="4"/>
       <c r="B82" s="5"/>
       <c r="C82" s="42"/>
@@ -2713,7 +2699,7 @@
       <c r="G82" s="6"/>
       <c r="H82" s="7"/>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A83" s="4"/>
       <c r="B83" s="5"/>
       <c r="C83" s="42"/>
@@ -2723,7 +2709,7 @@
       <c r="G83" s="6"/>
       <c r="H83" s="7"/>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A84" s="4"/>
       <c r="B84" s="5"/>
       <c r="C84" s="42"/>
@@ -2733,7 +2719,7 @@
       <c r="G84" s="6"/>
       <c r="H84" s="7"/>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A85" s="4"/>
       <c r="B85" s="5"/>
       <c r="C85" s="42"/>
@@ -2743,7 +2729,7 @@
       <c r="G85" s="6"/>
       <c r="H85" s="7"/>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A86" s="4"/>
       <c r="B86" s="5"/>
       <c r="C86" s="42"/>
@@ -2753,7 +2739,7 @@
       <c r="G86" s="6"/>
       <c r="H86" s="7"/>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A87" s="4"/>
       <c r="B87" s="5"/>
       <c r="C87" s="42"/>
@@ -2763,7 +2749,7 @@
       <c r="G87" s="6"/>
       <c r="H87" s="7"/>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A88" s="4"/>
       <c r="B88" s="5"/>
       <c r="C88" s="42"/>
@@ -2773,7 +2759,7 @@
       <c r="G88" s="6"/>
       <c r="H88" s="7"/>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A89" s="4"/>
       <c r="B89" s="5"/>
       <c r="C89" s="42"/>
@@ -2783,7 +2769,7 @@
       <c r="G89" s="6"/>
       <c r="H89" s="7"/>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A90" s="4"/>
       <c r="B90" s="5"/>
       <c r="C90" s="42"/>
@@ -2793,7 +2779,7 @@
       <c r="G90" s="6"/>
       <c r="H90" s="7"/>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A91" s="4"/>
       <c r="B91" s="5"/>
       <c r="C91" s="42"/>
@@ -2803,7 +2789,7 @@
       <c r="G91" s="6"/>
       <c r="H91" s="7"/>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A92" s="4"/>
       <c r="B92" s="5"/>
       <c r="C92" s="42"/>
@@ -2813,7 +2799,7 @@
       <c r="G92" s="6"/>
       <c r="H92" s="7"/>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A93" s="4"/>
       <c r="B93" s="5"/>
       <c r="C93" s="42"/>
@@ -2823,7 +2809,7 @@
       <c r="G93" s="6"/>
       <c r="H93" s="7"/>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A94" s="4"/>
       <c r="B94" s="5"/>
       <c r="C94" s="42"/>
@@ -2833,7 +2819,7 @@
       <c r="G94" s="6"/>
       <c r="H94" s="7"/>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A95" s="4"/>
       <c r="B95" s="5"/>
       <c r="C95" s="42"/>
@@ -2843,7 +2829,7 @@
       <c r="G95" s="6"/>
       <c r="H95" s="7"/>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A96" s="4"/>
       <c r="B96" s="5"/>
       <c r="C96" s="42"/>
@@ -2853,7 +2839,7 @@
       <c r="G96" s="6"/>
       <c r="H96" s="7"/>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A97" s="4"/>
       <c r="B97" s="5"/>
       <c r="C97" s="42"/>
@@ -2863,7 +2849,7 @@
       <c r="G97" s="6"/>
       <c r="H97" s="7"/>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A98" s="4"/>
       <c r="B98" s="5"/>
       <c r="C98" s="42"/>
@@ -2873,7 +2859,7 @@
       <c r="G98" s="6"/>
       <c r="H98" s="7"/>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A99" s="4"/>
       <c r="B99" s="5"/>
       <c r="C99" s="42"/>
@@ -2883,7 +2869,7 @@
       <c r="G99" s="6"/>
       <c r="H99" s="7"/>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A100" s="4"/>
       <c r="B100" s="5"/>
       <c r="C100" s="42"/>
@@ -2893,7 +2879,7 @@
       <c r="G100" s="6"/>
       <c r="H100" s="7"/>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A101" s="4"/>
       <c r="B101" s="5"/>
       <c r="C101" s="42"/>
@@ -2903,7 +2889,7 @@
       <c r="G101" s="6"/>
       <c r="H101" s="7"/>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A102" s="4"/>
       <c r="B102" s="5"/>
       <c r="C102" s="42"/>
@@ -2913,7 +2899,7 @@
       <c r="G102" s="6"/>
       <c r="H102" s="7"/>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A103" s="4"/>
       <c r="B103" s="5"/>
       <c r="C103" s="42"/>
@@ -2923,7 +2909,7 @@
       <c r="G103" s="6"/>
       <c r="H103" s="7"/>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A104" s="4"/>
       <c r="B104" s="5"/>
       <c r="C104" s="42"/>
@@ -2933,7 +2919,7 @@
       <c r="G104" s="6"/>
       <c r="H104" s="7"/>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A105" s="4"/>
       <c r="B105" s="5"/>
       <c r="C105" s="42"/>
@@ -2943,7 +2929,7 @@
       <c r="G105" s="6"/>
       <c r="H105" s="7"/>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A106" s="4"/>
       <c r="B106" s="5"/>
       <c r="C106" s="42"/>
@@ -2953,7 +2939,7 @@
       <c r="G106" s="6"/>
       <c r="H106" s="7"/>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A107" s="4"/>
       <c r="B107" s="5"/>
       <c r="C107" s="42"/>
@@ -2963,7 +2949,7 @@
       <c r="G107" s="6"/>
       <c r="H107" s="7"/>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A108" s="4"/>
       <c r="B108" s="5"/>
       <c r="C108" s="42"/>
@@ -2973,7 +2959,7 @@
       <c r="G108" s="6"/>
       <c r="H108" s="7"/>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A109" s="4"/>
       <c r="B109" s="5"/>
       <c r="C109" s="42"/>
@@ -2983,7 +2969,7 @@
       <c r="G109" s="6"/>
       <c r="H109" s="7"/>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A110" s="4"/>
       <c r="B110" s="5"/>
       <c r="C110" s="42"/>
@@ -2993,7 +2979,7 @@
       <c r="G110" s="6"/>
       <c r="H110" s="7"/>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A111" s="4"/>
       <c r="B111" s="5"/>
       <c r="C111" s="42"/>
@@ -3003,7 +2989,7 @@
       <c r="G111" s="6"/>
       <c r="H111" s="7"/>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A112" s="4"/>
       <c r="B112" s="5"/>
       <c r="C112" s="42"/>
@@ -3013,7 +2999,7 @@
       <c r="G112" s="6"/>
       <c r="H112" s="7"/>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A113" s="4"/>
       <c r="B113" s="5"/>
       <c r="C113" s="42"/>
@@ -3023,7 +3009,7 @@
       <c r="G113" s="6"/>
       <c r="H113" s="7"/>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A114" s="4"/>
       <c r="B114" s="5"/>
       <c r="C114" s="42"/>
@@ -3033,7 +3019,7 @@
       <c r="G114" s="6"/>
       <c r="H114" s="7"/>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A115" s="4"/>
       <c r="B115" s="5"/>
       <c r="C115" s="42"/>
@@ -3043,7 +3029,7 @@
       <c r="G115" s="6"/>
       <c r="H115" s="7"/>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A116" s="4"/>
       <c r="B116" s="5"/>
       <c r="C116" s="42"/>
@@ -3053,7 +3039,7 @@
       <c r="G116" s="6"/>
       <c r="H116" s="7"/>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A117" s="4"/>
       <c r="B117" s="5"/>
       <c r="C117" s="42"/>
@@ -3063,7 +3049,7 @@
       <c r="G117" s="6"/>
       <c r="H117" s="7"/>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A118" s="4"/>
       <c r="B118" s="5"/>
       <c r="C118" s="42"/>
@@ -3073,7 +3059,7 @@
       <c r="G118" s="6"/>
       <c r="H118" s="7"/>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A119" s="4"/>
       <c r="B119" s="5"/>
       <c r="C119" s="42"/>
@@ -3083,7 +3069,7 @@
       <c r="G119" s="6"/>
       <c r="H119" s="7"/>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A120" s="4"/>
       <c r="B120" s="5"/>
       <c r="C120" s="42"/>
@@ -3093,7 +3079,7 @@
       <c r="G120" s="6"/>
       <c r="H120" s="7"/>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A121" s="4"/>
       <c r="B121" s="5"/>
       <c r="C121" s="42"/>
@@ -3103,7 +3089,7 @@
       <c r="G121" s="6"/>
       <c r="H121" s="7"/>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A122" s="4"/>
       <c r="B122" s="5"/>
       <c r="C122" s="42"/>
@@ -3113,7 +3099,7 @@
       <c r="G122" s="6"/>
       <c r="H122" s="7"/>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A123" s="4"/>
       <c r="B123" s="5"/>
       <c r="C123" s="42"/>
@@ -3123,7 +3109,7 @@
       <c r="G123" s="6"/>
       <c r="H123" s="7"/>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A124" s="4"/>
       <c r="B124" s="5"/>
       <c r="C124" s="42"/>
@@ -3133,7 +3119,7 @@
       <c r="G124" s="6"/>
       <c r="H124" s="7"/>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A125" s="4"/>
       <c r="B125" s="5"/>
       <c r="C125" s="42"/>
@@ -3143,7 +3129,7 @@
       <c r="G125" s="6"/>
       <c r="H125" s="7"/>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A126" s="4"/>
       <c r="B126" s="5"/>
       <c r="C126" s="42"/>
@@ -3153,7 +3139,7 @@
       <c r="G126" s="6"/>
       <c r="H126" s="7"/>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A127" s="4"/>
       <c r="B127" s="5"/>
       <c r="C127" s="42"/>
@@ -3163,7 +3149,7 @@
       <c r="G127" s="6"/>
       <c r="H127" s="7"/>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A128" s="4"/>
       <c r="B128" s="5"/>
       <c r="C128" s="42"/>
@@ -3173,7 +3159,7 @@
       <c r="G128" s="6"/>
       <c r="H128" s="7"/>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A129" s="4"/>
       <c r="B129" s="5"/>
       <c r="C129" s="42"/>
@@ -3183,7 +3169,7 @@
       <c r="G129" s="6"/>
       <c r="H129" s="7"/>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A130" s="4"/>
       <c r="B130" s="5"/>
       <c r="C130" s="42"/>
@@ -3193,7 +3179,7 @@
       <c r="G130" s="6"/>
       <c r="H130" s="7"/>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A131" s="4"/>
       <c r="B131" s="5"/>
       <c r="C131" s="42"/>
@@ -3203,7 +3189,7 @@
       <c r="G131" s="6"/>
       <c r="H131" s="7"/>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A132" s="4"/>
       <c r="B132" s="5"/>
       <c r="C132" s="42"/>
@@ -3213,7 +3199,7 @@
       <c r="G132" s="6"/>
       <c r="H132" s="7"/>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A133" s="4"/>
       <c r="B133" s="5"/>
       <c r="C133" s="42"/>
@@ -3223,7 +3209,7 @@
       <c r="G133" s="6"/>
       <c r="H133" s="7"/>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A134" s="4"/>
       <c r="B134" s="5"/>
       <c r="C134" s="42"/>
@@ -3233,7 +3219,7 @@
       <c r="G134" s="6"/>
       <c r="H134" s="7"/>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A135" s="4"/>
       <c r="B135" s="5"/>
       <c r="C135" s="42"/>
@@ -3243,7 +3229,7 @@
       <c r="G135" s="6"/>
       <c r="H135" s="7"/>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A136" s="4"/>
       <c r="B136" s="5"/>
       <c r="C136" s="42"/>
@@ -3253,7 +3239,7 @@
       <c r="G136" s="6"/>
       <c r="H136" s="7"/>
     </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A137" s="4"/>
       <c r="B137" s="5"/>
       <c r="C137" s="42"/>
@@ -3263,7 +3249,7 @@
       <c r="G137" s="6"/>
       <c r="H137" s="7"/>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A138" s="4"/>
       <c r="B138" s="5"/>
       <c r="C138" s="42"/>
@@ -3273,7 +3259,7 @@
       <c r="G138" s="6"/>
       <c r="H138" s="7"/>
     </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A139" s="4"/>
       <c r="B139" s="5"/>
       <c r="C139" s="42"/>
@@ -3283,7 +3269,7 @@
       <c r="G139" s="6"/>
       <c r="H139" s="7"/>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A140" s="4"/>
       <c r="B140" s="5"/>
       <c r="C140" s="42"/>
@@ -3293,7 +3279,7 @@
       <c r="G140" s="6"/>
       <c r="H140" s="7"/>
     </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A141" s="4"/>
       <c r="B141" s="5"/>
       <c r="C141" s="42"/>
@@ -3303,7 +3289,7 @@
       <c r="G141" s="6"/>
       <c r="H141" s="7"/>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A142" s="4"/>
       <c r="B142" s="5"/>
       <c r="C142" s="42"/>
@@ -3313,7 +3299,7 @@
       <c r="G142" s="6"/>
       <c r="H142" s="7"/>
     </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A143" s="4"/>
       <c r="B143" s="5"/>
       <c r="C143" s="42"/>
@@ -3323,7 +3309,7 @@
       <c r="G143" s="6"/>
       <c r="H143" s="7"/>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A144" s="4"/>
       <c r="B144" s="5"/>
       <c r="C144" s="42"/>
@@ -3333,7 +3319,7 @@
       <c r="G144" s="6"/>
       <c r="H144" s="7"/>
     </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A145" s="4"/>
       <c r="B145" s="5"/>
       <c r="C145" s="42"/>
@@ -3343,7 +3329,7 @@
       <c r="G145" s="6"/>
       <c r="H145" s="7"/>
     </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A146" s="4"/>
       <c r="B146" s="5"/>
       <c r="C146" s="42"/>
@@ -3353,7 +3339,7 @@
       <c r="G146" s="6"/>
       <c r="H146" s="7"/>
     </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A147" s="4"/>
       <c r="B147" s="5"/>
       <c r="C147" s="42"/>
@@ -3363,7 +3349,7 @@
       <c r="G147" s="6"/>
       <c r="H147" s="7"/>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A148" s="4"/>
       <c r="B148" s="5"/>
       <c r="C148" s="42"/>
@@ -3373,7 +3359,7 @@
       <c r="G148" s="6"/>
       <c r="H148" s="7"/>
     </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A149" s="4"/>
       <c r="B149" s="5"/>
       <c r="C149" s="42"/>
@@ -3383,7 +3369,7 @@
       <c r="G149" s="6"/>
       <c r="H149" s="7"/>
     </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A150" s="4"/>
       <c r="B150" s="5"/>
       <c r="C150" s="42"/>
@@ -3393,7 +3379,7 @@
       <c r="G150" s="6"/>
       <c r="H150" s="7"/>
     </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A151" s="4"/>
       <c r="B151" s="5"/>
       <c r="C151" s="42"/>
@@ -3403,7 +3389,7 @@
       <c r="G151" s="6"/>
       <c r="H151" s="7"/>
     </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A152" s="4"/>
       <c r="B152" s="5"/>
       <c r="C152" s="42"/>
@@ -3413,7 +3399,7 @@
       <c r="G152" s="6"/>
       <c r="H152" s="7"/>
     </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A153" s="4"/>
       <c r="B153" s="5"/>
       <c r="C153" s="42"/>
@@ -3423,7 +3409,7 @@
       <c r="G153" s="6"/>
       <c r="H153" s="7"/>
     </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A154" s="4"/>
       <c r="B154" s="5"/>
       <c r="C154" s="42"/>
@@ -3433,7 +3419,7 @@
       <c r="G154" s="6"/>
       <c r="H154" s="7"/>
     </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A155" s="4"/>
       <c r="B155" s="5"/>
       <c r="C155" s="42"/>
@@ -3443,7 +3429,7 @@
       <c r="G155" s="6"/>
       <c r="H155" s="7"/>
     </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A156" s="4"/>
       <c r="B156" s="5"/>
       <c r="C156" s="42"/>
@@ -3453,7 +3439,7 @@
       <c r="G156" s="6"/>
       <c r="H156" s="7"/>
     </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A157" s="4"/>
       <c r="B157" s="5"/>
       <c r="C157" s="42"/>
@@ -3463,7 +3449,7 @@
       <c r="G157" s="6"/>
       <c r="H157" s="7"/>
     </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A158" s="4"/>
       <c r="B158" s="5"/>
       <c r="C158" s="42"/>
@@ -3473,7 +3459,7 @@
       <c r="G158" s="6"/>
       <c r="H158" s="7"/>
     </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A159" s="4"/>
       <c r="B159" s="5"/>
       <c r="C159" s="42"/>
@@ -3483,7 +3469,7 @@
       <c r="G159" s="6"/>
       <c r="H159" s="7"/>
     </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A160" s="4"/>
       <c r="B160" s="5"/>
       <c r="C160" s="42"/>
@@ -3493,7 +3479,7 @@
       <c r="G160" s="6"/>
       <c r="H160" s="7"/>
     </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A161" s="4"/>
       <c r="B161" s="5"/>
       <c r="C161" s="42"/>
@@ -3503,7 +3489,7 @@
       <c r="G161" s="6"/>
       <c r="H161" s="7"/>
     </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A162" s="4"/>
       <c r="B162" s="5"/>
       <c r="C162" s="42"/>
@@ -3513,7 +3499,7 @@
       <c r="G162" s="6"/>
       <c r="H162" s="7"/>
     </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A163" s="4"/>
       <c r="B163" s="5"/>
       <c r="C163" s="42"/>
@@ -3523,7 +3509,7 @@
       <c r="G163" s="6"/>
       <c r="H163" s="7"/>
     </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A164" s="4"/>
       <c r="B164" s="5"/>
       <c r="C164" s="42"/>
@@ -3533,7 +3519,7 @@
       <c r="G164" s="6"/>
       <c r="H164" s="7"/>
     </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A165" s="4"/>
       <c r="B165" s="5"/>
       <c r="C165" s="42"/>
@@ -3543,7 +3529,7 @@
       <c r="G165" s="6"/>
       <c r="H165" s="7"/>
     </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A166" s="4"/>
       <c r="B166" s="5"/>
       <c r="C166" s="42"/>
@@ -3553,7 +3539,7 @@
       <c r="G166" s="6"/>
       <c r="H166" s="7"/>
     </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A167" s="4"/>
       <c r="B167" s="5"/>
       <c r="C167" s="42"/>
@@ -3563,7 +3549,7 @@
       <c r="G167" s="6"/>
       <c r="H167" s="7"/>
     </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A168" s="4"/>
       <c r="B168" s="5"/>
       <c r="C168" s="42"/>
@@ -3573,7 +3559,7 @@
       <c r="G168" s="6"/>
       <c r="H168" s="7"/>
     </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A169" s="4"/>
       <c r="B169" s="5"/>
       <c r="C169" s="42"/>
@@ -3583,7 +3569,7 @@
       <c r="G169" s="6"/>
       <c r="H169" s="7"/>
     </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A170" s="4"/>
       <c r="B170" s="5"/>
       <c r="C170" s="42"/>
@@ -3593,7 +3579,7 @@
       <c r="G170" s="6"/>
       <c r="H170" s="7"/>
     </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A171" s="4"/>
       <c r="B171" s="5"/>
       <c r="C171" s="42"/>
@@ -3603,7 +3589,7 @@
       <c r="G171" s="6"/>
       <c r="H171" s="7"/>
     </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A172" s="4"/>
       <c r="B172" s="5"/>
       <c r="C172" s="42"/>
@@ -3613,7 +3599,7 @@
       <c r="G172" s="6"/>
       <c r="H172" s="7"/>
     </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A173" s="4"/>
       <c r="B173" s="5"/>
       <c r="C173" s="42"/>
@@ -3623,7 +3609,7 @@
       <c r="G173" s="6"/>
       <c r="H173" s="7"/>
     </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A174" s="4"/>
       <c r="B174" s="5"/>
       <c r="C174" s="42"/>
@@ -3633,7 +3619,7 @@
       <c r="G174" s="6"/>
       <c r="H174" s="7"/>
     </row>
-    <row r="175" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A175" s="4"/>
       <c r="B175" s="5"/>
       <c r="C175" s="42"/>
@@ -3643,7 +3629,7 @@
       <c r="G175" s="6"/>
       <c r="H175" s="7"/>
     </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A176" s="4"/>
       <c r="B176" s="5"/>
       <c r="C176" s="42"/>
@@ -3653,7 +3639,7 @@
       <c r="G176" s="6"/>
       <c r="H176" s="7"/>
     </row>
-    <row r="177" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A177" s="4"/>
       <c r="B177" s="5"/>
       <c r="C177" s="42"/>
@@ -3663,7 +3649,7 @@
       <c r="G177" s="6"/>
       <c r="H177" s="7"/>
     </row>
-    <row r="178" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A178" s="4"/>
       <c r="B178" s="5"/>
       <c r="C178" s="42"/>
@@ -3673,7 +3659,7 @@
       <c r="G178" s="6"/>
       <c r="H178" s="7"/>
     </row>
-    <row r="179" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A179" s="4"/>
       <c r="B179" s="5"/>
       <c r="C179" s="42"/>
@@ -3683,7 +3669,7 @@
       <c r="G179" s="6"/>
       <c r="H179" s="7"/>
     </row>
-    <row r="180" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A180" s="4"/>
       <c r="B180" s="5"/>
       <c r="C180" s="42"/>
@@ -3693,7 +3679,7 @@
       <c r="G180" s="6"/>
       <c r="H180" s="7"/>
     </row>
-    <row r="181" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A181" s="4"/>
       <c r="B181" s="5"/>
       <c r="C181" s="42"/>
@@ -3703,7 +3689,7 @@
       <c r="G181" s="6"/>
       <c r="H181" s="7"/>
     </row>
-    <row r="182" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A182" s="4"/>
       <c r="B182" s="5"/>
       <c r="C182" s="42"/>
@@ -3713,7 +3699,7 @@
       <c r="G182" s="6"/>
       <c r="H182" s="7"/>
     </row>
-    <row r="183" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A183" s="4"/>
       <c r="B183" s="5"/>
       <c r="C183" s="42"/>
@@ -3723,7 +3709,7 @@
       <c r="G183" s="6"/>
       <c r="H183" s="7"/>
     </row>
-    <row r="184" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A184" s="4"/>
       <c r="B184" s="5"/>
       <c r="C184" s="42"/>
@@ -3733,7 +3719,7 @@
       <c r="G184" s="6"/>
       <c r="H184" s="7"/>
     </row>
-    <row r="185" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A185" s="4"/>
       <c r="B185" s="5"/>
       <c r="C185" s="42"/>
@@ -3743,7 +3729,7 @@
       <c r="G185" s="6"/>
       <c r="H185" s="7"/>
     </row>
-    <row r="186" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A186" s="4"/>
       <c r="B186" s="5"/>
       <c r="C186" s="42"/>
@@ -3753,7 +3739,7 @@
       <c r="G186" s="6"/>
       <c r="H186" s="7"/>
     </row>
-    <row r="187" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A187" s="4"/>
       <c r="B187" s="5"/>
       <c r="C187" s="42"/>
@@ -3763,7 +3749,7 @@
       <c r="G187" s="6"/>
       <c r="H187" s="7"/>
     </row>
-    <row r="188" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A188" s="4"/>
       <c r="B188" s="5"/>
       <c r="C188" s="42"/>
@@ -3773,7 +3759,7 @@
       <c r="G188" s="6"/>
       <c r="H188" s="7"/>
     </row>
-    <row r="189" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A189" s="4"/>
       <c r="B189" s="5"/>
       <c r="C189" s="42"/>
@@ -3783,7 +3769,7 @@
       <c r="G189" s="6"/>
       <c r="H189" s="7"/>
     </row>
-    <row r="190" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A190" s="4"/>
       <c r="B190" s="5"/>
       <c r="C190" s="42"/>
@@ -3793,7 +3779,7 @@
       <c r="G190" s="6"/>
       <c r="H190" s="7"/>
     </row>
-    <row r="191" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A191" s="4"/>
       <c r="B191" s="5"/>
       <c r="C191" s="42"/>
@@ -3803,7 +3789,7 @@
       <c r="G191" s="6"/>
       <c r="H191" s="7"/>
     </row>
-    <row r="192" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A192" s="4"/>
       <c r="B192" s="5"/>
       <c r="C192" s="42"/>
@@ -3813,7 +3799,7 @@
       <c r="G192" s="6"/>
       <c r="H192" s="7"/>
     </row>
-    <row r="193" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A193" s="4"/>
       <c r="B193" s="5"/>
       <c r="C193" s="42"/>
@@ -3823,7 +3809,7 @@
       <c r="G193" s="6"/>
       <c r="H193" s="7"/>
     </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A194" s="4"/>
       <c r="B194" s="5"/>
       <c r="C194" s="42"/>
@@ -3833,7 +3819,7 @@
       <c r="G194" s="6"/>
       <c r="H194" s="7"/>
     </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A195" s="4"/>
       <c r="B195" s="5"/>
       <c r="C195" s="42"/>
@@ -3843,7 +3829,7 @@
       <c r="G195" s="6"/>
       <c r="H195" s="7"/>
     </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A196" s="4"/>
       <c r="B196" s="5"/>
       <c r="C196" s="42"/>
@@ -3853,7 +3839,7 @@
       <c r="G196" s="6"/>
       <c r="H196" s="7"/>
     </row>
-    <row r="197" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A197" s="4"/>
       <c r="B197" s="5"/>
       <c r="C197" s="42"/>
@@ -3863,7 +3849,7 @@
       <c r="G197" s="6"/>
       <c r="H197" s="7"/>
     </row>
-    <row r="198" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A198" s="4"/>
       <c r="B198" s="5"/>
       <c r="C198" s="42"/>
@@ -3873,7 +3859,7 @@
       <c r="G198" s="6"/>
       <c r="H198" s="7"/>
     </row>
-    <row r="199" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A199" s="4"/>
       <c r="B199" s="5"/>
       <c r="C199" s="42"/>
@@ -3883,7 +3869,7 @@
       <c r="G199" s="6"/>
       <c r="H199" s="7"/>
     </row>
-    <row r="200" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A200" s="4"/>
       <c r="B200" s="5"/>
       <c r="C200" s="42"/>
@@ -3893,7 +3879,7 @@
       <c r="G200" s="6"/>
       <c r="H200" s="7"/>
     </row>
-    <row r="201" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A201" s="4"/>
       <c r="B201" s="5"/>
       <c r="C201" s="42"/>
@@ -3903,7 +3889,7 @@
       <c r="G201" s="6"/>
       <c r="H201" s="7"/>
     </row>
-    <row r="202" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A202" s="4"/>
       <c r="B202" s="5"/>
       <c r="C202" s="42"/>
@@ -3913,7 +3899,7 @@
       <c r="G202" s="6"/>
       <c r="H202" s="7"/>
     </row>
-    <row r="203" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A203" s="4"/>
       <c r="B203" s="5"/>
       <c r="C203" s="42"/>
@@ -3923,7 +3909,7 @@
       <c r="G203" s="6"/>
       <c r="H203" s="7"/>
     </row>
-    <row r="204" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A204" s="4"/>
       <c r="B204" s="5"/>
       <c r="C204" s="42"/>
@@ -3933,7 +3919,7 @@
       <c r="G204" s="6"/>
       <c r="H204" s="7"/>
     </row>
-    <row r="205" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A205" s="4"/>
       <c r="B205" s="5"/>
       <c r="C205" s="42"/>
@@ -3943,7 +3929,7 @@
       <c r="G205" s="6"/>
       <c r="H205" s="7"/>
     </row>
-    <row r="206" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A206" s="4"/>
       <c r="B206" s="5"/>
       <c r="C206" s="42"/>
@@ -3953,7 +3939,7 @@
       <c r="G206" s="6"/>
       <c r="H206" s="7"/>
     </row>
-    <row r="207" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A207" s="4"/>
       <c r="B207" s="5"/>
       <c r="C207" s="42"/>
@@ -3963,7 +3949,7 @@
       <c r="G207" s="6"/>
       <c r="H207" s="7"/>
     </row>
-    <row r="208" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A208" s="4"/>
       <c r="B208" s="5"/>
       <c r="C208" s="42"/>
@@ -3973,7 +3959,7 @@
       <c r="G208" s="6"/>
       <c r="H208" s="7"/>
     </row>
-    <row r="209" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A209" s="4"/>
       <c r="B209" s="5"/>
       <c r="C209" s="42"/>
@@ -3983,7 +3969,7 @@
       <c r="G209" s="6"/>
       <c r="H209" s="7"/>
     </row>
-    <row r="210" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A210" s="4"/>
       <c r="B210" s="5"/>
       <c r="C210" s="42"/>
@@ -3993,7 +3979,7 @@
       <c r="G210" s="6"/>
       <c r="H210" s="7"/>
     </row>
-    <row r="211" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A211" s="4"/>
       <c r="B211" s="5"/>
       <c r="C211" s="42"/>
@@ -4003,7 +3989,7 @@
       <c r="G211" s="6"/>
       <c r="H211" s="7"/>
     </row>
-    <row r="212" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A212" s="4"/>
       <c r="B212" s="5"/>
       <c r="C212" s="42"/>
@@ -4013,7 +3999,7 @@
       <c r="G212" s="6"/>
       <c r="H212" s="7"/>
     </row>
-    <row r="213" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A213" s="4"/>
       <c r="B213" s="5"/>
       <c r="C213" s="42"/>
@@ -4023,7 +4009,7 @@
       <c r="G213" s="6"/>
       <c r="H213" s="7"/>
     </row>
-    <row r="214" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A214" s="4"/>
       <c r="B214" s="5"/>
       <c r="C214" s="42"/>
@@ -4033,7 +4019,7 @@
       <c r="G214" s="6"/>
       <c r="H214" s="7"/>
     </row>
-    <row r="215" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A215" s="4"/>
       <c r="B215" s="5"/>
       <c r="C215" s="42"/>
@@ -4043,7 +4029,7 @@
       <c r="G215" s="6"/>
       <c r="H215" s="7"/>
     </row>
-    <row r="216" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A216" s="4"/>
       <c r="B216" s="5"/>
       <c r="C216" s="42"/>
@@ -4053,7 +4039,7 @@
       <c r="G216" s="6"/>
       <c r="H216" s="7"/>
     </row>
-    <row r="217" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A217" s="4"/>
       <c r="B217" s="5"/>
       <c r="C217" s="42"/>
@@ -4063,7 +4049,7 @@
       <c r="G217" s="6"/>
       <c r="H217" s="7"/>
     </row>
-    <row r="218" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A218" s="4"/>
       <c r="B218" s="5"/>
       <c r="C218" s="42"/>
@@ -4073,7 +4059,7 @@
       <c r="G218" s="6"/>
       <c r="H218" s="7"/>
     </row>
-    <row r="219" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A219" s="4"/>
       <c r="B219" s="5"/>
       <c r="C219" s="42"/>
@@ -4083,7 +4069,7 @@
       <c r="G219" s="6"/>
       <c r="H219" s="7"/>
     </row>
-    <row r="220" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A220" s="4"/>
       <c r="B220" s="5"/>
       <c r="C220" s="42"/>
@@ -4093,7 +4079,7 @@
       <c r="G220" s="6"/>
       <c r="H220" s="7"/>
     </row>
-    <row r="221" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A221" s="4"/>
       <c r="B221" s="5"/>
       <c r="C221" s="42"/>
@@ -4103,7 +4089,7 @@
       <c r="G221" s="6"/>
       <c r="H221" s="7"/>
     </row>
-    <row r="222" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A222" s="4"/>
       <c r="B222" s="5"/>
       <c r="C222" s="42"/>
@@ -4113,7 +4099,7 @@
       <c r="G222" s="6"/>
       <c r="H222" s="7"/>
     </row>
-    <row r="223" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A223" s="4"/>
       <c r="B223" s="5"/>
       <c r="C223" s="42"/>
@@ -4123,7 +4109,7 @@
       <c r="G223" s="6"/>
       <c r="H223" s="7"/>
     </row>
-    <row r="224" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A224" s="4"/>
       <c r="B224" s="5"/>
       <c r="C224" s="42"/>
@@ -4133,7 +4119,7 @@
       <c r="G224" s="6"/>
       <c r="H224" s="7"/>
     </row>
-    <row r="225" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A225" s="4"/>
       <c r="B225" s="5"/>
       <c r="C225" s="42"/>
@@ -4143,7 +4129,7 @@
       <c r="G225" s="6"/>
       <c r="H225" s="7"/>
     </row>
-    <row r="226" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A226" s="4"/>
       <c r="B226" s="5"/>
       <c r="C226" s="42"/>
@@ -4153,7 +4139,7 @@
       <c r="G226" s="6"/>
       <c r="H226" s="7"/>
     </row>
-    <row r="227" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A227" s="4"/>
       <c r="B227" s="5"/>
       <c r="C227" s="42"/>
@@ -4163,7 +4149,7 @@
       <c r="G227" s="6"/>
       <c r="H227" s="7"/>
     </row>
-    <row r="228" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A228" s="4"/>
       <c r="B228" s="5"/>
       <c r="C228" s="42"/>
@@ -4173,7 +4159,7 @@
       <c r="G228" s="6"/>
       <c r="H228" s="7"/>
     </row>
-    <row r="229" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A229" s="4"/>
       <c r="B229" s="5"/>
       <c r="C229" s="42"/>
@@ -4183,7 +4169,7 @@
       <c r="G229" s="6"/>
       <c r="H229" s="7"/>
     </row>
-    <row r="230" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A230" s="4"/>
       <c r="B230" s="5"/>
       <c r="C230" s="42"/>
@@ -4193,7 +4179,7 @@
       <c r="G230" s="6"/>
       <c r="H230" s="7"/>
     </row>
-    <row r="231" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A231" s="4"/>
       <c r="B231" s="5"/>
       <c r="C231" s="42"/>
@@ -4203,7 +4189,7 @@
       <c r="G231" s="6"/>
       <c r="H231" s="7"/>
     </row>
-    <row r="232" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A232" s="4"/>
       <c r="B232" s="5"/>
       <c r="C232" s="42"/>
@@ -4213,7 +4199,7 @@
       <c r="G232" s="6"/>
       <c r="H232" s="7"/>
     </row>
-    <row r="233" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A233" s="4"/>
       <c r="B233" s="5"/>
       <c r="C233" s="42"/>
@@ -4223,7 +4209,7 @@
       <c r="G233" s="6"/>
       <c r="H233" s="7"/>
     </row>
-    <row r="234" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A234" s="4"/>
       <c r="B234" s="5"/>
       <c r="C234" s="42"/>
@@ -4233,7 +4219,7 @@
       <c r="G234" s="6"/>
       <c r="H234" s="7"/>
     </row>
-    <row r="235" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A235" s="4"/>
       <c r="B235" s="5"/>
       <c r="C235" s="42"/>
@@ -4243,7 +4229,7 @@
       <c r="G235" s="6"/>
       <c r="H235" s="7"/>
     </row>
-    <row r="236" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A236" s="4"/>
       <c r="B236" s="5"/>
       <c r="C236" s="42"/>
@@ -4253,7 +4239,7 @@
       <c r="G236" s="6"/>
       <c r="H236" s="7"/>
     </row>
-    <row r="237" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A237" s="4"/>
       <c r="B237" s="5"/>
       <c r="C237" s="42"/>
@@ -4263,7 +4249,7 @@
       <c r="G237" s="6"/>
       <c r="H237" s="7"/>
     </row>
-    <row r="238" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A238" s="4"/>
       <c r="B238" s="5"/>
       <c r="C238" s="42"/>
@@ -4273,7 +4259,7 @@
       <c r="G238" s="6"/>
       <c r="H238" s="7"/>
     </row>
-    <row r="239" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A239" s="4"/>
       <c r="B239" s="5"/>
       <c r="C239" s="42"/>
@@ -4283,7 +4269,7 @@
       <c r="G239" s="6"/>
       <c r="H239" s="7"/>
     </row>
-    <row r="240" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A240" s="4"/>
       <c r="B240" s="5"/>
       <c r="C240" s="42"/>
@@ -4293,7 +4279,7 @@
       <c r="G240" s="6"/>
       <c r="H240" s="7"/>
     </row>
-    <row r="241" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A241" s="4"/>
       <c r="B241" s="5"/>
       <c r="C241" s="42"/>
@@ -4303,7 +4289,7 @@
       <c r="G241" s="6"/>
       <c r="H241" s="7"/>
     </row>
-    <row r="242" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A242" s="4"/>
       <c r="B242" s="5"/>
       <c r="C242" s="42"/>
@@ -4313,7 +4299,7 @@
       <c r="G242" s="6"/>
       <c r="H242" s="7"/>
     </row>
-    <row r="243" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A243" s="4"/>
       <c r="B243" s="5"/>
       <c r="C243" s="42"/>
@@ -4323,7 +4309,7 @@
       <c r="G243" s="6"/>
       <c r="H243" s="7"/>
     </row>
-    <row r="244" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A244" s="4"/>
       <c r="B244" s="5"/>
       <c r="C244" s="42"/>
@@ -4333,7 +4319,7 @@
       <c r="G244" s="6"/>
       <c r="H244" s="7"/>
     </row>
-    <row r="245" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A245" s="4"/>
       <c r="B245" s="5"/>
       <c r="C245" s="42"/>
@@ -4343,7 +4329,7 @@
       <c r="G245" s="6"/>
       <c r="H245" s="7"/>
     </row>
-    <row r="246" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A246" s="4"/>
       <c r="B246" s="5"/>
       <c r="C246" s="42"/>
@@ -4353,7 +4339,7 @@
       <c r="G246" s="6"/>
       <c r="H246" s="7"/>
     </row>
-    <row r="247" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A247" s="4"/>
       <c r="B247" s="5"/>
       <c r="C247" s="42"/>
@@ -4363,7 +4349,7 @@
       <c r="G247" s="6"/>
       <c r="H247" s="7"/>
     </row>
-    <row r="248" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A248" s="4"/>
       <c r="B248" s="5"/>
       <c r="C248" s="42"/>
@@ -4373,7 +4359,7 @@
       <c r="G248" s="6"/>
       <c r="H248" s="7"/>
     </row>
-    <row r="249" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A249" s="4"/>
       <c r="B249" s="5"/>
       <c r="C249" s="42"/>
@@ -4383,7 +4369,7 @@
       <c r="G249" s="6"/>
       <c r="H249" s="7"/>
     </row>
-    <row r="250" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A250" s="4"/>
       <c r="B250" s="5"/>
       <c r="C250" s="42"/>
@@ -4393,7 +4379,7 @@
       <c r="G250" s="6"/>
       <c r="H250" s="7"/>
     </row>
-    <row r="251" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A251" s="4"/>
       <c r="B251" s="5"/>
       <c r="C251" s="42"/>
@@ -4403,7 +4389,7 @@
       <c r="G251" s="6"/>
       <c r="H251" s="7"/>
     </row>
-    <row r="252" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A252" s="4"/>
       <c r="B252" s="5"/>
       <c r="C252" s="42"/>
@@ -4413,7 +4399,7 @@
       <c r="G252" s="6"/>
       <c r="H252" s="7"/>
     </row>
-    <row r="253" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A253" s="4"/>
       <c r="B253" s="5"/>
       <c r="C253" s="42"/>
@@ -4423,7 +4409,7 @@
       <c r="G253" s="6"/>
       <c r="H253" s="7"/>
     </row>
-    <row r="254" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A254" s="4"/>
       <c r="B254" s="5"/>
       <c r="C254" s="42"/>
@@ -4433,7 +4419,7 @@
       <c r="G254" s="6"/>
       <c r="H254" s="7"/>
     </row>
-    <row r="255" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A255" s="4"/>
       <c r="B255" s="5"/>
       <c r="C255" s="42"/>
@@ -4443,7 +4429,7 @@
       <c r="G255" s="6"/>
       <c r="H255" s="7"/>
     </row>
-    <row r="256" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A256" s="4"/>
       <c r="B256" s="5"/>
       <c r="C256" s="42"/>
@@ -4453,7 +4439,7 @@
       <c r="G256" s="6"/>
       <c r="H256" s="7"/>
     </row>
-    <row r="257" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A257" s="4"/>
       <c r="B257" s="5"/>
       <c r="C257" s="42"/>
@@ -4463,7 +4449,7 @@
       <c r="G257" s="6"/>
       <c r="H257" s="7"/>
     </row>
-    <row r="258" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A258" s="4"/>
       <c r="B258" s="5"/>
       <c r="C258" s="42"/>
@@ -4473,7 +4459,7 @@
       <c r="G258" s="6"/>
       <c r="H258" s="7"/>
     </row>
-    <row r="259" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A259" s="4"/>
       <c r="B259" s="5"/>
       <c r="C259" s="42"/>
@@ -4483,7 +4469,7 @@
       <c r="G259" s="6"/>
       <c r="H259" s="7"/>
     </row>
-    <row r="260" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A260" s="4"/>
       <c r="B260" s="5"/>
       <c r="C260" s="42"/>
@@ -4493,7 +4479,7 @@
       <c r="G260" s="6"/>
       <c r="H260" s="7"/>
     </row>
-    <row r="261" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A261" s="4"/>
       <c r="B261" s="5"/>
       <c r="C261" s="42"/>
@@ -4503,7 +4489,7 @@
       <c r="G261" s="6"/>
       <c r="H261" s="7"/>
     </row>
-    <row r="262" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A262" s="4"/>
       <c r="B262" s="5"/>
       <c r="C262" s="42"/>
@@ -4513,7 +4499,7 @@
       <c r="G262" s="6"/>
       <c r="H262" s="7"/>
     </row>
-    <row r="263" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A263" s="4"/>
       <c r="B263" s="5"/>
       <c r="C263" s="42"/>
@@ -4523,7 +4509,7 @@
       <c r="G263" s="6"/>
       <c r="H263" s="7"/>
     </row>
-    <row r="264" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A264" s="4"/>
       <c r="B264" s="5"/>
       <c r="C264" s="42"/>
@@ -4533,7 +4519,7 @@
       <c r="G264" s="6"/>
       <c r="H264" s="7"/>
     </row>
-    <row r="265" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A265" s="4"/>
       <c r="B265" s="5"/>
       <c r="C265" s="42"/>
@@ -4543,7 +4529,7 @@
       <c r="G265" s="6"/>
       <c r="H265" s="7"/>
     </row>
-    <row r="266" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A266" s="4"/>
       <c r="B266" s="5"/>
       <c r="C266" s="42"/>
@@ -4553,7 +4539,7 @@
       <c r="G266" s="6"/>
       <c r="H266" s="7"/>
     </row>
-    <row r="267" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A267" s="4"/>
       <c r="B267" s="5"/>
       <c r="C267" s="42"/>
@@ -4563,7 +4549,7 @@
       <c r="G267" s="6"/>
       <c r="H267" s="7"/>
     </row>
-    <row r="268" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A268" s="4"/>
       <c r="B268" s="5"/>
       <c r="C268" s="42"/>
@@ -4573,7 +4559,7 @@
       <c r="G268" s="6"/>
       <c r="H268" s="7"/>
     </row>
-    <row r="269" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A269" s="4"/>
       <c r="B269" s="5"/>
       <c r="C269" s="42"/>
@@ -4583,7 +4569,7 @@
       <c r="G269" s="6"/>
       <c r="H269" s="7"/>
     </row>
-    <row r="270" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A270" s="4"/>
       <c r="B270" s="5"/>
       <c r="C270" s="42"/>
@@ -4593,7 +4579,7 @@
       <c r="G270" s="6"/>
       <c r="H270" s="7"/>
     </row>
-    <row r="271" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A271" s="4"/>
       <c r="B271" s="5"/>
       <c r="C271" s="42"/>
@@ -4603,7 +4589,7 @@
       <c r="G271" s="6"/>
       <c r="H271" s="7"/>
     </row>
-    <row r="272" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A272" s="4"/>
       <c r="B272" s="5"/>
       <c r="C272" s="42"/>
@@ -4613,7 +4599,7 @@
       <c r="G272" s="6"/>
       <c r="H272" s="7"/>
     </row>
-    <row r="273" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A273" s="4"/>
       <c r="B273" s="5"/>
       <c r="C273" s="42"/>
@@ -4623,7 +4609,7 @@
       <c r="G273" s="6"/>
       <c r="H273" s="7"/>
     </row>
-    <row r="274" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A274" s="4"/>
       <c r="B274" s="5"/>
       <c r="C274" s="42"/>
@@ -4633,7 +4619,7 @@
       <c r="G274" s="6"/>
       <c r="H274" s="7"/>
     </row>
-    <row r="275" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A275" s="4"/>
       <c r="B275" s="5"/>
       <c r="C275" s="42"/>
@@ -4643,7 +4629,7 @@
       <c r="G275" s="6"/>
       <c r="H275" s="7"/>
     </row>
-    <row r="276" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A276" s="4"/>
       <c r="B276" s="5"/>
       <c r="C276" s="42"/>
@@ -4653,7 +4639,7 @@
       <c r="G276" s="6"/>
       <c r="H276" s="7"/>
     </row>
-    <row r="277" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A277" s="4"/>
       <c r="B277" s="5"/>
       <c r="C277" s="42"/>
@@ -4663,7 +4649,7 @@
       <c r="G277" s="6"/>
       <c r="H277" s="7"/>
     </row>
-    <row r="278" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A278" s="4"/>
       <c r="B278" s="5"/>
       <c r="C278" s="42"/>
@@ -4673,7 +4659,7 @@
       <c r="G278" s="6"/>
       <c r="H278" s="7"/>
     </row>
-    <row r="279" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A279" s="4"/>
       <c r="B279" s="5"/>
       <c r="C279" s="42"/>
@@ -4683,7 +4669,7 @@
       <c r="G279" s="6"/>
       <c r="H279" s="7"/>
     </row>
-    <row r="280" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A280" s="4"/>
       <c r="B280" s="5"/>
       <c r="C280" s="42"/>
@@ -4693,7 +4679,7 @@
       <c r="G280" s="6"/>
       <c r="H280" s="7"/>
     </row>
-    <row r="281" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A281" s="4"/>
       <c r="B281" s="5"/>
       <c r="C281" s="42"/>
@@ -4703,7 +4689,7 @@
       <c r="G281" s="6"/>
       <c r="H281" s="7"/>
     </row>
-    <row r="282" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A282" s="4"/>
       <c r="B282" s="5"/>
       <c r="C282" s="42"/>
@@ -4713,7 +4699,7 @@
       <c r="G282" s="6"/>
       <c r="H282" s="7"/>
     </row>
-    <row r="283" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A283" s="4"/>
       <c r="B283" s="5"/>
       <c r="C283" s="42"/>
@@ -4723,7 +4709,7 @@
       <c r="G283" s="6"/>
       <c r="H283" s="7"/>
     </row>
-    <row r="284" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A284" s="4"/>
       <c r="B284" s="5"/>
       <c r="C284" s="42"/>
@@ -4733,7 +4719,7 @@
       <c r="G284" s="6"/>
       <c r="H284" s="7"/>
     </row>
-    <row r="285" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A285" s="4"/>
       <c r="B285" s="5"/>
       <c r="C285" s="42"/>
@@ -4743,7 +4729,7 @@
       <c r="G285" s="6"/>
       <c r="H285" s="7"/>
     </row>
-    <row r="286" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A286" s="4"/>
       <c r="B286" s="5"/>
       <c r="C286" s="42"/>
@@ -4753,7 +4739,7 @@
       <c r="G286" s="6"/>
       <c r="H286" s="7"/>
     </row>
-    <row r="287" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A287" s="4"/>
       <c r="B287" s="5"/>
       <c r="C287" s="42"/>
@@ -4763,7 +4749,7 @@
       <c r="G287" s="6"/>
       <c r="H287" s="7"/>
     </row>
-    <row r="288" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A288" s="4"/>
       <c r="B288" s="5"/>
       <c r="C288" s="42"/>
@@ -4773,7 +4759,7 @@
       <c r="G288" s="6"/>
       <c r="H288" s="7"/>
     </row>
-    <row r="289" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A289" s="4"/>
       <c r="B289" s="5"/>
       <c r="C289" s="42"/>
@@ -4783,7 +4769,7 @@
       <c r="G289" s="6"/>
       <c r="H289" s="7"/>
     </row>
-    <row r="290" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A290" s="4"/>
       <c r="B290" s="5"/>
       <c r="C290" s="42"/>
@@ -4793,7 +4779,7 @@
       <c r="G290" s="6"/>
       <c r="H290" s="7"/>
     </row>
-    <row r="291" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A291" s="4"/>
       <c r="B291" s="5"/>
       <c r="C291" s="42"/>
@@ -4803,7 +4789,7 @@
       <c r="G291" s="6"/>
       <c r="H291" s="7"/>
     </row>
-    <row r="292" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A292" s="4"/>
       <c r="B292" s="5"/>
       <c r="C292" s="42"/>
@@ -4813,7 +4799,7 @@
       <c r="G292" s="6"/>
       <c r="H292" s="7"/>
     </row>
-    <row r="293" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A293" s="4"/>
       <c r="B293" s="5"/>
       <c r="C293" s="42"/>
@@ -4823,7 +4809,7 @@
       <c r="G293" s="6"/>
       <c r="H293" s="7"/>
     </row>
-    <row r="294" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A294" s="4"/>
       <c r="B294" s="5"/>
       <c r="C294" s="42"/>
@@ -4833,7 +4819,7 @@
       <c r="G294" s="6"/>
       <c r="H294" s="7"/>
     </row>
-    <row r="295" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A295" s="4"/>
       <c r="B295" s="5"/>
       <c r="C295" s="42"/>
@@ -4843,7 +4829,7 @@
       <c r="G295" s="6"/>
       <c r="H295" s="7"/>
     </row>
-    <row r="296" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A296" s="4"/>
       <c r="B296" s="5"/>
       <c r="C296" s="42"/>
@@ -4853,7 +4839,7 @@
       <c r="G296" s="6"/>
       <c r="H296" s="7"/>
     </row>
-    <row r="297" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A297" s="4"/>
       <c r="B297" s="5"/>
       <c r="C297" s="42"/>
@@ -4863,7 +4849,7 @@
       <c r="G297" s="6"/>
       <c r="H297" s="7"/>
     </row>
-    <row r="298" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A298" s="4"/>
       <c r="B298" s="5"/>
       <c r="C298" s="42"/>
@@ -4873,7 +4859,7 @@
       <c r="G298" s="6"/>
       <c r="H298" s="7"/>
     </row>
-    <row r="299" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A299" s="4"/>
       <c r="B299" s="5"/>
       <c r="C299" s="42"/>
@@ -4883,7 +4869,7 @@
       <c r="G299" s="6"/>
       <c r="H299" s="7"/>
     </row>
-    <row r="300" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A300" s="4"/>
       <c r="B300" s="5"/>
       <c r="C300" s="42"/>
@@ -4893,7 +4879,7 @@
       <c r="G300" s="6"/>
       <c r="H300" s="7"/>
     </row>
-    <row r="301" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A301" s="4"/>
       <c r="B301" s="5"/>
       <c r="C301" s="42"/>
@@ -4903,7 +4889,7 @@
       <c r="G301" s="6"/>
       <c r="H301" s="7"/>
     </row>
-    <row r="302" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A302" s="4"/>
       <c r="B302" s="5"/>
       <c r="C302" s="42"/>
@@ -4913,7 +4899,7 @@
       <c r="G302" s="6"/>
       <c r="H302" s="7"/>
     </row>
-    <row r="303" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A303" s="4"/>
       <c r="B303" s="5"/>
       <c r="C303" s="42"/>
@@ -4923,7 +4909,7 @@
       <c r="G303" s="6"/>
       <c r="H303" s="7"/>
     </row>
-    <row r="304" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A304" s="4"/>
       <c r="B304" s="5"/>
       <c r="C304" s="42"/>
@@ -4933,7 +4919,7 @@
       <c r="G304" s="6"/>
       <c r="H304" s="7"/>
     </row>
-    <row r="305" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A305" s="4"/>
       <c r="B305" s="5"/>
       <c r="C305" s="42"/>
@@ -4943,7 +4929,7 @@
       <c r="G305" s="6"/>
       <c r="H305" s="7"/>
     </row>
-    <row r="306" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A306" s="4"/>
       <c r="B306" s="5"/>
       <c r="C306" s="42"/>
@@ -4953,7 +4939,7 @@
       <c r="G306" s="6"/>
       <c r="H306" s="7"/>
     </row>
-    <row r="307" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A307" s="4"/>
       <c r="B307" s="5"/>
       <c r="C307" s="42"/>
@@ -4963,7 +4949,7 @@
       <c r="G307" s="6"/>
       <c r="H307" s="7"/>
     </row>
-    <row r="308" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A308" s="4"/>
       <c r="B308" s="5"/>
       <c r="C308" s="42"/>
@@ -4973,7 +4959,7 @@
       <c r="G308" s="6"/>
       <c r="H308" s="7"/>
     </row>
-    <row r="309" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A309" s="4"/>
       <c r="B309" s="5"/>
       <c r="C309" s="42"/>
@@ -4983,7 +4969,7 @@
       <c r="G309" s="6"/>
       <c r="H309" s="7"/>
     </row>
-    <row r="310" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A310" s="4"/>
       <c r="B310" s="5"/>
       <c r="C310" s="42"/>
@@ -4993,7 +4979,7 @@
       <c r="G310" s="6"/>
       <c r="H310" s="7"/>
     </row>
-    <row r="311" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A311" s="4"/>
       <c r="B311" s="5"/>
       <c r="C311" s="42"/>
@@ -5003,7 +4989,7 @@
       <c r="G311" s="6"/>
       <c r="H311" s="7"/>
     </row>
-    <row r="312" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A312" s="4"/>
       <c r="B312" s="5"/>
       <c r="C312" s="42"/>
@@ -5013,7 +4999,7 @@
       <c r="G312" s="6"/>
       <c r="H312" s="7"/>
     </row>
-    <row r="313" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A313" s="4"/>
       <c r="B313" s="5"/>
       <c r="C313" s="42"/>
@@ -5023,7 +5009,7 @@
       <c r="G313" s="6"/>
       <c r="H313" s="7"/>
     </row>
-    <row r="314" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A314" s="4"/>
       <c r="B314" s="5"/>
       <c r="C314" s="42"/>
@@ -5033,7 +5019,7 @@
       <c r="G314" s="6"/>
       <c r="H314" s="7"/>
     </row>
-    <row r="315" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A315" s="4"/>
       <c r="B315" s="5"/>
       <c r="C315" s="42"/>
@@ -5043,7 +5029,7 @@
       <c r="G315" s="6"/>
       <c r="H315" s="7"/>
     </row>
-    <row r="316" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A316" s="4"/>
       <c r="B316" s="5"/>
       <c r="C316" s="42"/>
@@ -5053,7 +5039,7 @@
       <c r="G316" s="6"/>
       <c r="H316" s="7"/>
     </row>
-    <row r="317" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A317" s="4"/>
       <c r="B317" s="5"/>
       <c r="C317" s="42"/>
@@ -5063,7 +5049,7 @@
       <c r="G317" s="6"/>
       <c r="H317" s="7"/>
     </row>
-    <row r="318" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A318" s="4"/>
       <c r="B318" s="5"/>
       <c r="C318" s="42"/>
@@ -5073,7 +5059,7 @@
       <c r="G318" s="6"/>
       <c r="H318" s="7"/>
     </row>
-    <row r="319" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A319" s="4"/>
       <c r="B319" s="5"/>
       <c r="C319" s="42"/>
@@ -5083,7 +5069,7 @@
       <c r="G319" s="6"/>
       <c r="H319" s="7"/>
     </row>
-    <row r="320" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A320" s="4"/>
       <c r="B320" s="5"/>
       <c r="C320" s="42"/>
@@ -5093,7 +5079,7 @@
       <c r="G320" s="6"/>
       <c r="H320" s="7"/>
     </row>
-    <row r="321" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A321" s="4"/>
       <c r="B321" s="5"/>
       <c r="C321" s="42"/>
@@ -5103,7 +5089,7 @@
       <c r="G321" s="6"/>
       <c r="H321" s="7"/>
     </row>
-    <row r="322" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A322" s="4"/>
       <c r="B322" s="5"/>
       <c r="C322" s="42"/>
@@ -5113,7 +5099,7 @@
       <c r="G322" s="6"/>
       <c r="H322" s="7"/>
     </row>
-    <row r="323" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A323" s="4"/>
       <c r="B323" s="5"/>
       <c r="C323" s="42"/>
@@ -5123,7 +5109,7 @@
       <c r="G323" s="6"/>
       <c r="H323" s="7"/>
     </row>
-    <row r="324" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A324" s="4"/>
       <c r="B324" s="5"/>
       <c r="C324" s="42"/>
@@ -5133,7 +5119,7 @@
       <c r="G324" s="6"/>
       <c r="H324" s="7"/>
     </row>
-    <row r="325" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A325" s="4"/>
       <c r="B325" s="5"/>
       <c r="C325" s="42"/>
@@ -5143,7 +5129,7 @@
       <c r="G325" s="6"/>
       <c r="H325" s="7"/>
     </row>
-    <row r="326" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A326" s="4"/>
       <c r="B326" s="5"/>
       <c r="C326" s="42"/>
@@ -5153,7 +5139,7 @@
       <c r="G326" s="6"/>
       <c r="H326" s="7"/>
     </row>
-    <row r="327" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A327" s="4"/>
       <c r="B327" s="5"/>
       <c r="C327" s="42"/>
@@ -5163,7 +5149,7 @@
       <c r="G327" s="6"/>
       <c r="H327" s="7"/>
     </row>
-    <row r="328" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A328" s="4"/>
       <c r="B328" s="5"/>
       <c r="C328" s="42"/>
@@ -5173,7 +5159,7 @@
       <c r="G328" s="6"/>
       <c r="H328" s="7"/>
     </row>
-    <row r="329" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A329" s="4"/>
       <c r="B329" s="5"/>
       <c r="C329" s="42"/>
@@ -5183,7 +5169,7 @@
       <c r="G329" s="6"/>
       <c r="H329" s="7"/>
     </row>
-    <row r="330" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A330" s="4"/>
       <c r="B330" s="5"/>
       <c r="C330" s="42"/>
@@ -5193,7 +5179,7 @@
       <c r="G330" s="6"/>
       <c r="H330" s="7"/>
     </row>
-    <row r="331" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A331" s="4"/>
       <c r="B331" s="5"/>
       <c r="C331" s="42"/>
@@ -5203,7 +5189,7 @@
       <c r="G331" s="6"/>
       <c r="H331" s="7"/>
     </row>
-    <row r="332" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A332" s="4"/>
       <c r="B332" s="5"/>
       <c r="C332" s="42"/>
@@ -5213,7 +5199,7 @@
       <c r="G332" s="6"/>
       <c r="H332" s="7"/>
     </row>
-    <row r="333" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A333" s="4"/>
       <c r="B333" s="5"/>
       <c r="C333" s="42"/>
@@ -5223,7 +5209,7 @@
       <c r="G333" s="6"/>
       <c r="H333" s="7"/>
     </row>
-    <row r="334" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A334" s="4"/>
       <c r="B334" s="5"/>
       <c r="C334" s="42"/>
@@ -5233,7 +5219,7 @@
       <c r="G334" s="6"/>
       <c r="H334" s="7"/>
     </row>
-    <row r="335" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A335" s="4"/>
       <c r="B335" s="5"/>
       <c r="C335" s="42"/>
@@ -5243,7 +5229,7 @@
       <c r="G335" s="6"/>
       <c r="H335" s="7"/>
     </row>
-    <row r="336" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A336" s="4"/>
       <c r="B336" s="5"/>
       <c r="C336" s="42"/>
@@ -5253,7 +5239,7 @@
       <c r="G336" s="6"/>
       <c r="H336" s="7"/>
     </row>
-    <row r="337" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A337" s="4"/>
       <c r="B337" s="5"/>
       <c r="C337" s="42"/>
@@ -5263,7 +5249,7 @@
       <c r="G337" s="6"/>
       <c r="H337" s="7"/>
     </row>
-    <row r="338" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A338" s="4"/>
       <c r="B338" s="5"/>
       <c r="C338" s="42"/>
@@ -5273,7 +5259,7 @@
       <c r="G338" s="6"/>
       <c r="H338" s="7"/>
     </row>
-    <row r="339" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A339" s="4"/>
       <c r="B339" s="5"/>
       <c r="C339" s="42"/>
@@ -5283,7 +5269,7 @@
       <c r="G339" s="6"/>
       <c r="H339" s="7"/>
     </row>
-    <row r="340" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A340" s="4"/>
       <c r="B340" s="5"/>
       <c r="C340" s="42"/>
@@ -5293,7 +5279,7 @@
       <c r="G340" s="6"/>
       <c r="H340" s="7"/>
     </row>
-    <row r="341" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A341" s="4"/>
       <c r="B341" s="5"/>
       <c r="C341" s="42"/>
@@ -5303,7 +5289,7 @@
       <c r="G341" s="6"/>
       <c r="H341" s="7"/>
     </row>
-    <row r="342" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A342" s="4"/>
       <c r="B342" s="5"/>
       <c r="C342" s="42"/>
@@ -5313,7 +5299,7 @@
       <c r="G342" s="6"/>
       <c r="H342" s="7"/>
     </row>
-    <row r="343" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A343" s="4"/>
       <c r="B343" s="5"/>
       <c r="C343" s="42"/>
@@ -5323,7 +5309,7 @@
       <c r="G343" s="6"/>
       <c r="H343" s="7"/>
     </row>
-    <row r="344" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A344" s="4"/>
       <c r="B344" s="5"/>
       <c r="C344" s="42"/>
@@ -5333,7 +5319,7 @@
       <c r="G344" s="6"/>
       <c r="H344" s="7"/>
     </row>
-    <row r="345" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A345" s="4"/>
       <c r="B345" s="5"/>
       <c r="C345" s="42"/>
@@ -5343,7 +5329,7 @@
       <c r="G345" s="6"/>
       <c r="H345" s="7"/>
     </row>
-    <row r="346" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A346" s="4"/>
       <c r="B346" s="5"/>
       <c r="C346" s="42"/>
@@ -5353,7 +5339,7 @@
       <c r="G346" s="6"/>
       <c r="H346" s="7"/>
     </row>
-    <row r="347" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A347" s="4"/>
       <c r="B347" s="5"/>
       <c r="C347" s="42"/>
@@ -5363,7 +5349,7 @@
       <c r="G347" s="6"/>
       <c r="H347" s="7"/>
     </row>
-    <row r="348" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A348" s="4"/>
       <c r="B348" s="5"/>
       <c r="C348" s="42"/>
@@ -5373,7 +5359,7 @@
       <c r="G348" s="6"/>
       <c r="H348" s="7"/>
     </row>
-    <row r="349" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A349" s="4"/>
       <c r="B349" s="5"/>
       <c r="C349" s="42"/>
@@ -5383,7 +5369,7 @@
       <c r="G349" s="6"/>
       <c r="H349" s="7"/>
     </row>
-    <row r="350" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A350" s="4"/>
       <c r="B350" s="5"/>
       <c r="C350" s="42"/>
@@ -5393,7 +5379,7 @@
       <c r="G350" s="6"/>
       <c r="H350" s="7"/>
     </row>
-    <row r="351" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A351" s="4"/>
       <c r="B351" s="5"/>
       <c r="C351" s="42"/>
@@ -5403,7 +5389,7 @@
       <c r="G351" s="6"/>
       <c r="H351" s="7"/>
     </row>
-    <row r="352" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A352" s="4"/>
       <c r="B352" s="5"/>
       <c r="C352" s="42"/>
@@ -5413,7 +5399,7 @@
       <c r="G352" s="6"/>
       <c r="H352" s="7"/>
     </row>
-    <row r="353" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A353" s="4"/>
       <c r="B353" s="5"/>
       <c r="C353" s="42"/>
@@ -5423,7 +5409,7 @@
       <c r="G353" s="6"/>
       <c r="H353" s="7"/>
     </row>
-    <row r="354" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A354" s="4"/>
       <c r="B354" s="5"/>
       <c r="C354" s="42"/>
@@ -5433,7 +5419,7 @@
       <c r="G354" s="6"/>
       <c r="H354" s="7"/>
     </row>
-    <row r="355" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A355" s="4"/>
       <c r="B355" s="5"/>
       <c r="C355" s="42"/>
@@ -5443,7 +5429,7 @@
       <c r="G355" s="6"/>
       <c r="H355" s="7"/>
     </row>
-    <row r="356" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A356" s="4"/>
       <c r="B356" s="5"/>
       <c r="C356" s="42"/>
@@ -5453,7 +5439,7 @@
       <c r="G356" s="6"/>
       <c r="H356" s="7"/>
     </row>
-    <row r="357" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A357" s="4"/>
       <c r="B357" s="5"/>
       <c r="C357" s="42"/>
@@ -5463,7 +5449,7 @@
       <c r="G357" s="6"/>
       <c r="H357" s="7"/>
     </row>
-    <row r="358" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A358" s="4"/>
       <c r="B358" s="5"/>
       <c r="C358" s="42"/>
@@ -5473,7 +5459,7 @@
       <c r="G358" s="6"/>
       <c r="H358" s="7"/>
     </row>
-    <row r="359" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A359" s="4"/>
       <c r="B359" s="5"/>
       <c r="C359" s="42"/>
@@ -5483,7 +5469,7 @@
       <c r="G359" s="6"/>
       <c r="H359" s="7"/>
     </row>
-    <row r="360" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A360" s="4"/>
       <c r="B360" s="5"/>
       <c r="C360" s="42"/>
@@ -5493,7 +5479,7 @@
       <c r="G360" s="6"/>
       <c r="H360" s="7"/>
     </row>
-    <row r="361" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A361" s="4"/>
       <c r="B361" s="5"/>
       <c r="C361" s="42"/>
@@ -5503,7 +5489,7 @@
       <c r="G361" s="6"/>
       <c r="H361" s="7"/>
     </row>
-    <row r="362" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A362" s="4"/>
       <c r="B362" s="5"/>
       <c r="C362" s="42"/>
@@ -5513,7 +5499,7 @@
       <c r="G362" s="6"/>
       <c r="H362" s="7"/>
     </row>
-    <row r="363" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A363" s="4"/>
       <c r="B363" s="5"/>
       <c r="C363" s="42"/>
@@ -5523,7 +5509,7 @@
       <c r="G363" s="6"/>
       <c r="H363" s="7"/>
     </row>
-    <row r="364" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A364" s="4"/>
       <c r="B364" s="5"/>
       <c r="C364" s="42"/>
@@ -5533,7 +5519,7 @@
       <c r="G364" s="6"/>
       <c r="H364" s="7"/>
     </row>
-    <row r="365" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A365" s="4"/>
       <c r="B365" s="5"/>
       <c r="C365" s="42"/>
@@ -5543,7 +5529,7 @@
       <c r="G365" s="6"/>
       <c r="H365" s="7"/>
     </row>
-    <row r="366" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A366" s="4"/>
       <c r="B366" s="5"/>
       <c r="C366" s="42"/>
@@ -5553,7 +5539,7 @@
       <c r="G366" s="6"/>
       <c r="H366" s="7"/>
     </row>
-    <row r="367" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A367" s="4"/>
       <c r="B367" s="5"/>
       <c r="C367" s="42"/>
@@ -5563,7 +5549,7 @@
       <c r="G367" s="6"/>
       <c r="H367" s="7"/>
     </row>
-    <row r="368" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A368" s="4"/>
       <c r="B368" s="5"/>
       <c r="C368" s="42"/>
@@ -5573,7 +5559,7 @@
       <c r="G368" s="6"/>
       <c r="H368" s="7"/>
     </row>
-    <row r="369" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A369" s="4"/>
       <c r="B369" s="5"/>
       <c r="C369" s="42"/>
@@ -5583,7 +5569,7 @@
       <c r="G369" s="6"/>
       <c r="H369" s="7"/>
     </row>
-    <row r="370" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A370" s="4"/>
       <c r="B370" s="5"/>
       <c r="C370" s="42"/>
@@ -5593,7 +5579,7 @@
       <c r="G370" s="6"/>
       <c r="H370" s="7"/>
     </row>
-    <row r="371" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A371" s="4"/>
       <c r="B371" s="5"/>
       <c r="C371" s="42"/>
@@ -5603,7 +5589,7 @@
       <c r="G371" s="6"/>
       <c r="H371" s="7"/>
     </row>
-    <row r="372" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A372" s="4"/>
       <c r="B372" s="5"/>
       <c r="C372" s="42"/>
@@ -5613,7 +5599,7 @@
       <c r="G372" s="6"/>
       <c r="H372" s="7"/>
     </row>
-    <row r="373" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A373" s="4"/>
       <c r="B373" s="5"/>
       <c r="C373" s="42"/>
@@ -5623,7 +5609,7 @@
       <c r="G373" s="6"/>
       <c r="H373" s="7"/>
     </row>
-    <row r="374" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A374" s="4"/>
       <c r="B374" s="5"/>
       <c r="C374" s="42"/>
@@ -5633,7 +5619,7 @@
       <c r="G374" s="6"/>
       <c r="H374" s="7"/>
     </row>
-    <row r="375" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A375" s="4"/>
       <c r="B375" s="5"/>
       <c r="C375" s="42"/>
@@ -5643,7 +5629,7 @@
       <c r="G375" s="6"/>
       <c r="H375" s="7"/>
     </row>
-    <row r="376" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A376" s="4"/>
       <c r="B376" s="5"/>
       <c r="C376" s="42"/>
@@ -5653,7 +5639,7 @@
       <c r="G376" s="6"/>
       <c r="H376" s="7"/>
     </row>
-    <row r="377" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A377" s="4"/>
       <c r="B377" s="5"/>
       <c r="C377" s="42"/>
@@ -5663,7 +5649,7 @@
       <c r="G377" s="6"/>
       <c r="H377" s="7"/>
     </row>
-    <row r="378" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A378" s="4"/>
       <c r="B378" s="5"/>
       <c r="C378" s="42"/>
@@ -5673,7 +5659,7 @@
       <c r="G378" s="6"/>
       <c r="H378" s="7"/>
     </row>
-    <row r="379" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A379" s="4"/>
       <c r="B379" s="5"/>
       <c r="C379" s="42"/>
@@ -5683,7 +5669,7 @@
       <c r="G379" s="6"/>
       <c r="H379" s="7"/>
     </row>
-    <row r="380" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A380" s="4"/>
       <c r="B380" s="5"/>
       <c r="C380" s="42"/>
@@ -5693,7 +5679,7 @@
       <c r="G380" s="6"/>
       <c r="H380" s="7"/>
     </row>
-    <row r="381" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A381" s="4"/>
       <c r="B381" s="5"/>
       <c r="C381" s="42"/>
@@ -5703,7 +5689,7 @@
       <c r="G381" s="6"/>
       <c r="H381" s="7"/>
     </row>
-    <row r="382" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A382" s="4"/>
       <c r="B382" s="5"/>
       <c r="C382" s="42"/>
@@ -5713,7 +5699,7 @@
       <c r="G382" s="6"/>
       <c r="H382" s="7"/>
     </row>
-    <row r="383" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A383" s="4"/>
       <c r="B383" s="5"/>
       <c r="C383" s="42"/>
@@ -5723,7 +5709,7 @@
       <c r="G383" s="6"/>
       <c r="H383" s="7"/>
     </row>
-    <row r="384" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A384" s="4"/>
       <c r="B384" s="5"/>
       <c r="C384" s="42"/>
@@ -5733,7 +5719,7 @@
       <c r="G384" s="6"/>
       <c r="H384" s="7"/>
     </row>
-    <row r="385" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A385" s="4"/>
       <c r="B385" s="5"/>
       <c r="C385" s="42"/>
@@ -5743,7 +5729,7 @@
       <c r="G385" s="6"/>
       <c r="H385" s="7"/>
     </row>
-    <row r="386" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A386" s="4"/>
       <c r="B386" s="5"/>
       <c r="C386" s="42"/>
@@ -5753,7 +5739,7 @@
       <c r="G386" s="6"/>
       <c r="H386" s="7"/>
     </row>
-    <row r="387" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A387" s="4"/>
       <c r="B387" s="5"/>
       <c r="C387" s="42"/>
@@ -5763,7 +5749,7 @@
       <c r="G387" s="6"/>
       <c r="H387" s="7"/>
     </row>
-    <row r="388" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A388" s="4"/>
       <c r="B388" s="5"/>
       <c r="C388" s="42"/>
@@ -5773,7 +5759,7 @@
       <c r="G388" s="6"/>
       <c r="H388" s="7"/>
     </row>
-    <row r="389" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A389" s="4"/>
       <c r="B389" s="5"/>
       <c r="C389" s="42"/>
@@ -5783,7 +5769,7 @@
       <c r="G389" s="6"/>
       <c r="H389" s="7"/>
     </row>
-    <row r="390" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A390" s="4"/>
       <c r="B390" s="5"/>
       <c r="C390" s="42"/>
@@ -5793,7 +5779,7 @@
       <c r="G390" s="6"/>
       <c r="H390" s="7"/>
     </row>
-    <row r="391" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A391" s="4"/>
       <c r="B391" s="5"/>
       <c r="C391" s="42"/>
@@ -5803,7 +5789,7 @@
       <c r="G391" s="6"/>
       <c r="H391" s="7"/>
     </row>
-    <row r="392" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A392" s="4"/>
       <c r="B392" s="5"/>
       <c r="C392" s="42"/>
@@ -5813,7 +5799,7 @@
       <c r="G392" s="6"/>
       <c r="H392" s="7"/>
     </row>
-    <row r="393" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A393" s="4"/>
       <c r="B393" s="5"/>
       <c r="C393" s="42"/>
@@ -5823,7 +5809,7 @@
       <c r="G393" s="6"/>
       <c r="H393" s="7"/>
     </row>
-    <row r="394" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A394" s="4"/>
       <c r="B394" s="5"/>
       <c r="C394" s="42"/>
@@ -5833,7 +5819,7 @@
       <c r="G394" s="6"/>
       <c r="H394" s="7"/>
     </row>
-    <row r="395" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A395" s="4"/>
       <c r="B395" s="5"/>
       <c r="C395" s="42"/>
@@ -5843,7 +5829,7 @@
       <c r="G395" s="6"/>
       <c r="H395" s="7"/>
     </row>
-    <row r="396" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A396" s="4"/>
       <c r="B396" s="5"/>
       <c r="C396" s="42"/>
@@ -5853,7 +5839,7 @@
       <c r="G396" s="6"/>
       <c r="H396" s="7"/>
     </row>
-    <row r="397" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A397" s="4"/>
       <c r="B397" s="5"/>
       <c r="C397" s="42"/>
@@ -5863,7 +5849,7 @@
       <c r="G397" s="6"/>
       <c r="H397" s="7"/>
     </row>
-    <row r="398" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A398" s="4"/>
       <c r="B398" s="5"/>
       <c r="C398" s="42"/>
@@ -5873,7 +5859,7 @@
       <c r="G398" s="6"/>
       <c r="H398" s="7"/>
     </row>
-    <row r="399" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A399" s="4"/>
       <c r="B399" s="5"/>
       <c r="C399" s="42"/>
@@ -5883,7 +5869,7 @@
       <c r="G399" s="6"/>
       <c r="H399" s="7"/>
     </row>
-    <row r="400" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A400" s="4"/>
       <c r="B400" s="5"/>
       <c r="C400" s="42"/>
@@ -5893,7 +5879,7 @@
       <c r="G400" s="6"/>
       <c r="H400" s="7"/>
     </row>
-    <row r="401" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A401" s="4"/>
       <c r="B401" s="5"/>
       <c r="C401" s="42"/>
@@ -5903,7 +5889,7 @@
       <c r="G401" s="6"/>
       <c r="H401" s="7"/>
     </row>
-    <row r="402" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A402" s="4"/>
       <c r="B402" s="5"/>
       <c r="C402" s="42"/>
@@ -5913,7 +5899,7 @@
       <c r="G402" s="6"/>
       <c r="H402" s="7"/>
     </row>
-    <row r="403" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A403" s="4"/>
       <c r="B403" s="5"/>
       <c r="C403" s="42"/>
@@ -5923,7 +5909,7 @@
       <c r="G403" s="6"/>
       <c r="H403" s="7"/>
     </row>
-    <row r="404" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A404" s="4"/>
       <c r="B404" s="5"/>
       <c r="C404" s="42"/>
@@ -5933,7 +5919,7 @@
       <c r="G404" s="6"/>
       <c r="H404" s="7"/>
     </row>
-    <row r="405" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A405" s="4"/>
       <c r="B405" s="5"/>
       <c r="C405" s="42"/>
@@ -5943,7 +5929,7 @@
       <c r="G405" s="6"/>
       <c r="H405" s="7"/>
     </row>
-    <row r="406" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A406" s="4"/>
       <c r="B406" s="5"/>
       <c r="C406" s="42"/>
@@ -5953,7 +5939,7 @@
       <c r="G406" s="6"/>
       <c r="H406" s="7"/>
     </row>
-    <row r="407" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A407" s="4"/>
       <c r="B407" s="5"/>
       <c r="C407" s="42"/>
@@ -5963,7 +5949,7 @@
       <c r="G407" s="6"/>
       <c r="H407" s="7"/>
     </row>
-    <row r="408" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A408" s="4"/>
       <c r="B408" s="5"/>
       <c r="C408" s="42"/>
@@ -5973,7 +5959,7 @@
       <c r="G408" s="6"/>
       <c r="H408" s="7"/>
     </row>
-    <row r="409" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A409" s="4"/>
       <c r="B409" s="5"/>
       <c r="C409" s="42"/>
@@ -5983,7 +5969,7 @@
       <c r="G409" s="6"/>
       <c r="H409" s="7"/>
     </row>
-    <row r="410" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A410" s="4"/>
       <c r="B410" s="5"/>
       <c r="C410" s="42"/>
@@ -5993,7 +5979,7 @@
       <c r="G410" s="6"/>
       <c r="H410" s="7"/>
     </row>
-    <row r="411" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A411" s="8"/>
       <c r="B411" s="9"/>
       <c r="C411" s="10"/>
@@ -6005,24 +5991,24 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C6:H6"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="C4:D4"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C6:H6"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="C4:D4"/>
   </mergeCells>
   <conditionalFormatting sqref="A8:B411">
-    <cfRule type="expression" dxfId="6" priority="2">
+    <cfRule type="expression" dxfId="4" priority="2">
       <formula>MOD(ROW()-1,2)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8:H411">
-    <cfRule type="expression" dxfId="5" priority="1">
+    <cfRule type="expression" dxfId="3" priority="1">
       <formula>MOD(ROW()-1,2)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6058,77 +6044,77 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D4F706A-7CC7-470C-8128-D48A70DD74AB}">
   <dimension ref="A1:H409"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="22.7109375" customWidth="1"/>
-    <col min="3" max="4" width="22.7109375" style="2" customWidth="1"/>
-    <col min="5" max="5" width="25.28515625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="45.7109375" style="2" customWidth="1"/>
-    <col min="7" max="7" width="35.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.28515625" customWidth="1"/>
+    <col min="1" max="2" width="22.6640625" customWidth="1"/>
+    <col min="3" max="4" width="22.6640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="25.33203125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="45.6640625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="35.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="45" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="45"/>
-      <c r="C1" s="51" t="s">
+      <c r="C1" s="52" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="52"/>
+      <c r="D1" s="53"/>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="45" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="45"/>
-      <c r="C2" s="51" t="s">
+      <c r="C2" s="52" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="52"/>
+      <c r="D2" s="53"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="45" t="s">
         <v>5</v>
       </c>
       <c r="B3" s="45"/>
-      <c r="C3" s="51" t="s">
+      <c r="C3" s="52" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="52"/>
+      <c r="D3" s="53"/>
       <c r="E3" s="3"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="45" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="45"/>
-      <c r="C4" s="51" t="s">
+      <c r="C4" s="52" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="52"/>
+      <c r="D4" s="53"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="49" t="s">
+    <row r="5" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="48" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="50"/>
-      <c r="C6" s="47" t="str">
+      <c r="B6" s="49"/>
+      <c r="C6" s="50" t="str">
         <f>"Collaborator Table - "&amp;C1&amp;" ("&amp;C2&amp;")"</f>
         <v>Collaborator Table - University of XYZ (Jones, Jane)</v>
       </c>
-      <c r="D6" s="47"/>
-      <c r="E6" s="47"/>
-      <c r="F6" s="47"/>
-      <c r="G6" s="47"/>
-      <c r="H6" s="48"/>
-    </row>
-    <row r="7" spans="1:8" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D6" s="50"/>
+      <c r="E6" s="50"/>
+      <c r="F6" s="50"/>
+      <c r="G6" s="50"/>
+      <c r="H6" s="51"/>
+    </row>
+    <row r="7" spans="1:8" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="20" t="s">
         <v>8</v>
       </c>
@@ -6154,7 +6140,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
         <v>18</v>
       </c>
@@ -6180,7 +6166,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>18</v>
       </c>
@@ -6206,7 +6192,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
         <v>18</v>
       </c>
@@ -6232,7 +6218,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
         <v>35</v>
       </c>
@@ -6258,7 +6244,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
         <v>35</v>
       </c>
@@ -6284,7 +6270,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="4"/>
       <c r="B13" s="5"/>
       <c r="C13" s="42"/>
@@ -6294,7 +6280,7 @@
       <c r="G13" s="6"/>
       <c r="H13" s="7"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="4"/>
       <c r="B14" s="5"/>
       <c r="C14" s="42"/>
@@ -6304,7 +6290,7 @@
       <c r="G14" s="6"/>
       <c r="H14" s="7"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="4"/>
       <c r="B15" s="5"/>
       <c r="C15" s="42"/>
@@ -6314,7 +6300,7 @@
       <c r="G15" s="6"/>
       <c r="H15" s="7"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="4"/>
       <c r="B16" s="5"/>
       <c r="C16" s="42"/>
@@ -6324,7 +6310,7 @@
       <c r="G16" s="6"/>
       <c r="H16" s="7"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="4"/>
       <c r="B17" s="5"/>
       <c r="C17" s="42"/>
@@ -6334,7 +6320,7 @@
       <c r="G17" s="6"/>
       <c r="H17" s="7"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="4"/>
       <c r="B18" s="5"/>
       <c r="C18" s="42"/>
@@ -6344,7 +6330,7 @@
       <c r="G18" s="6"/>
       <c r="H18" s="7"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="4"/>
       <c r="B19" s="5"/>
       <c r="C19" s="42"/>
@@ -6354,7 +6340,7 @@
       <c r="G19" s="6"/>
       <c r="H19" s="7"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="4"/>
       <c r="B20" s="5"/>
       <c r="C20" s="42"/>
@@ -6364,7 +6350,7 @@
       <c r="G20" s="6"/>
       <c r="H20" s="7"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="4"/>
       <c r="B21" s="5"/>
       <c r="C21" s="42"/>
@@ -6374,7 +6360,7 @@
       <c r="G21" s="6"/>
       <c r="H21" s="7"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="4"/>
       <c r="B22" s="5"/>
       <c r="C22" s="42"/>
@@ -6384,7 +6370,7 @@
       <c r="G22" s="6"/>
       <c r="H22" s="7"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" s="4"/>
       <c r="B23" s="5"/>
       <c r="C23" s="42"/>
@@ -6394,7 +6380,7 @@
       <c r="G23" s="6"/>
       <c r="H23" s="7"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" s="4"/>
       <c r="B24" s="5"/>
       <c r="C24" s="42"/>
@@ -6404,7 +6390,7 @@
       <c r="G24" s="6"/>
       <c r="H24" s="7"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="4"/>
       <c r="B25" s="5"/>
       <c r="C25" s="42"/>
@@ -6414,7 +6400,7 @@
       <c r="G25" s="6"/>
       <c r="H25" s="7"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" s="4"/>
       <c r="B26" s="5"/>
       <c r="C26" s="42"/>
@@ -6424,7 +6410,7 @@
       <c r="G26" s="6"/>
       <c r="H26" s="7"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" s="4"/>
       <c r="B27" s="5"/>
       <c r="C27" s="42"/>
@@ -6434,7 +6420,7 @@
       <c r="G27" s="6"/>
       <c r="H27" s="7"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="4"/>
       <c r="B28" s="5"/>
       <c r="C28" s="42"/>
@@ -6444,7 +6430,7 @@
       <c r="G28" s="6"/>
       <c r="H28" s="7"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="4"/>
       <c r="B29" s="5"/>
       <c r="C29" s="42"/>
@@ -6454,7 +6440,7 @@
       <c r="G29" s="6"/>
       <c r="H29" s="7"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="4"/>
       <c r="B30" s="5"/>
       <c r="C30" s="42"/>
@@ -6464,7 +6450,7 @@
       <c r="G30" s="6"/>
       <c r="H30" s="7"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="4"/>
       <c r="B31" s="5"/>
       <c r="C31" s="42"/>
@@ -6474,7 +6460,7 @@
       <c r="G31" s="6"/>
       <c r="H31" s="7"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" s="4"/>
       <c r="B32" s="5"/>
       <c r="C32" s="42"/>
@@ -6484,7 +6470,7 @@
       <c r="G32" s="6"/>
       <c r="H32" s="7"/>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" s="4"/>
       <c r="B33" s="5"/>
       <c r="C33" s="42"/>
@@ -6494,7 +6480,7 @@
       <c r="G33" s="6"/>
       <c r="H33" s="7"/>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" s="4"/>
       <c r="B34" s="5"/>
       <c r="C34" s="42"/>
@@ -6504,7 +6490,7 @@
       <c r="G34" s="6"/>
       <c r="H34" s="7"/>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" s="4"/>
       <c r="B35" s="5"/>
       <c r="C35" s="42"/>
@@ -6514,7 +6500,7 @@
       <c r="G35" s="6"/>
       <c r="H35" s="7"/>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" s="4"/>
       <c r="B36" s="5"/>
       <c r="C36" s="42"/>
@@ -6524,7 +6510,7 @@
       <c r="G36" s="6"/>
       <c r="H36" s="7"/>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" s="4"/>
       <c r="B37" s="5"/>
       <c r="C37" s="42"/>
@@ -6534,7 +6520,7 @@
       <c r="G37" s="6"/>
       <c r="H37" s="7"/>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" s="4"/>
       <c r="B38" s="5"/>
       <c r="C38" s="42"/>
@@ -6544,7 +6530,7 @@
       <c r="G38" s="6"/>
       <c r="H38" s="7"/>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" s="4"/>
       <c r="B39" s="5"/>
       <c r="C39" s="42"/>
@@ -6554,7 +6540,7 @@
       <c r="G39" s="6"/>
       <c r="H39" s="7"/>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" s="4"/>
       <c r="B40" s="5"/>
       <c r="C40" s="42"/>
@@ -6564,7 +6550,7 @@
       <c r="G40" s="6"/>
       <c r="H40" s="7"/>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" s="4"/>
       <c r="B41" s="5"/>
       <c r="C41" s="42"/>
@@ -6574,7 +6560,7 @@
       <c r="G41" s="6"/>
       <c r="H41" s="7"/>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" s="4"/>
       <c r="B42" s="5"/>
       <c r="C42" s="42"/>
@@ -6584,7 +6570,7 @@
       <c r="G42" s="6"/>
       <c r="H42" s="7"/>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" s="4"/>
       <c r="B43" s="5"/>
       <c r="C43" s="42"/>
@@ -6594,7 +6580,7 @@
       <c r="G43" s="6"/>
       <c r="H43" s="7"/>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" s="4"/>
       <c r="B44" s="5"/>
       <c r="C44" s="42"/>
@@ -6604,7 +6590,7 @@
       <c r="G44" s="6"/>
       <c r="H44" s="7"/>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" s="4"/>
       <c r="B45" s="5"/>
       <c r="C45" s="42"/>
@@ -6614,7 +6600,7 @@
       <c r="G45" s="6"/>
       <c r="H45" s="7"/>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" s="4"/>
       <c r="B46" s="5"/>
       <c r="C46" s="42"/>
@@ -6624,7 +6610,7 @@
       <c r="G46" s="6"/>
       <c r="H46" s="7"/>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" s="4"/>
       <c r="B47" s="5"/>
       <c r="C47" s="42"/>
@@ -6634,7 +6620,7 @@
       <c r="G47" s="6"/>
       <c r="H47" s="7"/>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" s="4"/>
       <c r="B48" s="5"/>
       <c r="C48" s="42"/>
@@ -6644,7 +6630,7 @@
       <c r="G48" s="6"/>
       <c r="H48" s="7"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" s="4"/>
       <c r="B49" s="5"/>
       <c r="C49" s="42"/>
@@ -6654,7 +6640,7 @@
       <c r="G49" s="6"/>
       <c r="H49" s="7"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" s="4"/>
       <c r="B50" s="5"/>
       <c r="C50" s="42"/>
@@ -6664,7 +6650,7 @@
       <c r="G50" s="6"/>
       <c r="H50" s="7"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" s="4"/>
       <c r="B51" s="5"/>
       <c r="C51" s="42"/>
@@ -6674,7 +6660,7 @@
       <c r="G51" s="6"/>
       <c r="H51" s="7"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" s="4"/>
       <c r="B52" s="5"/>
       <c r="C52" s="42"/>
@@ -6684,7 +6670,7 @@
       <c r="G52" s="6"/>
       <c r="H52" s="7"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53" s="4"/>
       <c r="B53" s="5"/>
       <c r="C53" s="42"/>
@@ -6694,7 +6680,7 @@
       <c r="G53" s="6"/>
       <c r="H53" s="7"/>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54" s="4"/>
       <c r="B54" s="5"/>
       <c r="C54" s="42"/>
@@ -6704,7 +6690,7 @@
       <c r="G54" s="6"/>
       <c r="H54" s="7"/>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A55" s="4"/>
       <c r="B55" s="5"/>
       <c r="C55" s="42"/>
@@ -6714,7 +6700,7 @@
       <c r="G55" s="6"/>
       <c r="H55" s="7"/>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A56" s="4"/>
       <c r="B56" s="5"/>
       <c r="C56" s="42"/>
@@ -6724,7 +6710,7 @@
       <c r="G56" s="6"/>
       <c r="H56" s="7"/>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A57" s="4"/>
       <c r="B57" s="5"/>
       <c r="C57" s="42"/>
@@ -6734,7 +6720,7 @@
       <c r="G57" s="6"/>
       <c r="H57" s="7"/>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A58" s="4"/>
       <c r="B58" s="5"/>
       <c r="C58" s="42"/>
@@ -6744,7 +6730,7 @@
       <c r="G58" s="6"/>
       <c r="H58" s="7"/>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A59" s="4"/>
       <c r="B59" s="5"/>
       <c r="C59" s="42"/>
@@ -6754,7 +6740,7 @@
       <c r="G59" s="6"/>
       <c r="H59" s="7"/>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A60" s="4"/>
       <c r="B60" s="5"/>
       <c r="C60" s="42"/>
@@ -6764,7 +6750,7 @@
       <c r="G60" s="6"/>
       <c r="H60" s="7"/>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A61" s="4"/>
       <c r="B61" s="5"/>
       <c r="C61" s="42"/>
@@ -6774,7 +6760,7 @@
       <c r="G61" s="6"/>
       <c r="H61" s="7"/>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A62" s="4"/>
       <c r="B62" s="5"/>
       <c r="C62" s="42"/>
@@ -6784,7 +6770,7 @@
       <c r="G62" s="6"/>
       <c r="H62" s="7"/>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A63" s="4"/>
       <c r="B63" s="5"/>
       <c r="C63" s="42"/>
@@ -6794,7 +6780,7 @@
       <c r="G63" s="6"/>
       <c r="H63" s="7"/>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A64" s="4"/>
       <c r="B64" s="5"/>
       <c r="C64" s="42"/>
@@ -6804,7 +6790,7 @@
       <c r="G64" s="6"/>
       <c r="H64" s="7"/>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A65" s="4"/>
       <c r="B65" s="5"/>
       <c r="C65" s="42"/>
@@ -6814,7 +6800,7 @@
       <c r="G65" s="6"/>
       <c r="H65" s="7"/>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A66" s="4"/>
       <c r="B66" s="5"/>
       <c r="C66" s="42"/>
@@ -6824,7 +6810,7 @@
       <c r="G66" s="6"/>
       <c r="H66" s="7"/>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A67" s="4"/>
       <c r="B67" s="5"/>
       <c r="C67" s="42"/>
@@ -6834,7 +6820,7 @@
       <c r="G67" s="6"/>
       <c r="H67" s="7"/>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A68" s="4"/>
       <c r="B68" s="5"/>
       <c r="C68" s="42"/>
@@ -6844,7 +6830,7 @@
       <c r="G68" s="6"/>
       <c r="H68" s="7"/>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A69" s="4"/>
       <c r="B69" s="5"/>
       <c r="C69" s="42"/>
@@ -6854,7 +6840,7 @@
       <c r="G69" s="6"/>
       <c r="H69" s="7"/>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A70" s="4"/>
       <c r="B70" s="5"/>
       <c r="C70" s="42"/>
@@ -6864,7 +6850,7 @@
       <c r="G70" s="6"/>
       <c r="H70" s="7"/>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A71" s="4"/>
       <c r="B71" s="5"/>
       <c r="C71" s="42"/>
@@ -6874,7 +6860,7 @@
       <c r="G71" s="6"/>
       <c r="H71" s="7"/>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A72" s="4"/>
       <c r="B72" s="5"/>
       <c r="C72" s="42"/>
@@ -6884,7 +6870,7 @@
       <c r="G72" s="6"/>
       <c r="H72" s="7"/>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A73" s="4"/>
       <c r="B73" s="5"/>
       <c r="C73" s="42"/>
@@ -6894,7 +6880,7 @@
       <c r="G73" s="6"/>
       <c r="H73" s="7"/>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A74" s="4"/>
       <c r="B74" s="5"/>
       <c r="C74" s="42"/>
@@ -6904,7 +6890,7 @@
       <c r="G74" s="6"/>
       <c r="H74" s="7"/>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A75" s="4"/>
       <c r="B75" s="5"/>
       <c r="C75" s="42"/>
@@ -6914,7 +6900,7 @@
       <c r="G75" s="6"/>
       <c r="H75" s="7"/>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A76" s="4"/>
       <c r="B76" s="5"/>
       <c r="C76" s="42"/>
@@ -6924,7 +6910,7 @@
       <c r="G76" s="6"/>
       <c r="H76" s="7"/>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A77" s="4"/>
       <c r="B77" s="5"/>
       <c r="C77" s="42"/>
@@ -6934,7 +6920,7 @@
       <c r="G77" s="6"/>
       <c r="H77" s="7"/>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A78" s="4"/>
       <c r="B78" s="5"/>
       <c r="C78" s="42"/>
@@ -6944,7 +6930,7 @@
       <c r="G78" s="6"/>
       <c r="H78" s="7"/>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A79" s="4"/>
       <c r="B79" s="5"/>
       <c r="C79" s="42"/>
@@ -6954,7 +6940,7 @@
       <c r="G79" s="6"/>
       <c r="H79" s="7"/>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A80" s="4"/>
       <c r="B80" s="5"/>
       <c r="C80" s="42"/>
@@ -6964,7 +6950,7 @@
       <c r="G80" s="6"/>
       <c r="H80" s="7"/>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A81" s="4"/>
       <c r="B81" s="5"/>
       <c r="C81" s="42"/>
@@ -6974,7 +6960,7 @@
       <c r="G81" s="6"/>
       <c r="H81" s="7"/>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A82" s="4"/>
       <c r="B82" s="5"/>
       <c r="C82" s="42"/>
@@ -6984,7 +6970,7 @@
       <c r="G82" s="6"/>
       <c r="H82" s="7"/>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A83" s="4"/>
       <c r="B83" s="5"/>
       <c r="C83" s="42"/>
@@ -6994,7 +6980,7 @@
       <c r="G83" s="6"/>
       <c r="H83" s="7"/>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A84" s="4"/>
       <c r="B84" s="5"/>
       <c r="C84" s="42"/>
@@ -7004,7 +6990,7 @@
       <c r="G84" s="6"/>
       <c r="H84" s="7"/>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A85" s="4"/>
       <c r="B85" s="5"/>
       <c r="C85" s="42"/>
@@ -7014,7 +7000,7 @@
       <c r="G85" s="6"/>
       <c r="H85" s="7"/>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A86" s="4"/>
       <c r="B86" s="5"/>
       <c r="C86" s="42"/>
@@ -7024,7 +7010,7 @@
       <c r="G86" s="6"/>
       <c r="H86" s="7"/>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A87" s="4"/>
       <c r="B87" s="5"/>
       <c r="C87" s="42"/>
@@ -7034,7 +7020,7 @@
       <c r="G87" s="6"/>
       <c r="H87" s="7"/>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A88" s="4"/>
       <c r="B88" s="5"/>
       <c r="C88" s="42"/>
@@ -7044,7 +7030,7 @@
       <c r="G88" s="6"/>
       <c r="H88" s="7"/>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A89" s="4"/>
       <c r="B89" s="5"/>
       <c r="C89" s="42"/>
@@ -7054,7 +7040,7 @@
       <c r="G89" s="6"/>
       <c r="H89" s="7"/>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A90" s="4"/>
       <c r="B90" s="5"/>
       <c r="C90" s="42"/>
@@ -7064,7 +7050,7 @@
       <c r="G90" s="6"/>
       <c r="H90" s="7"/>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A91" s="4"/>
       <c r="B91" s="5"/>
       <c r="C91" s="42"/>
@@ -7074,7 +7060,7 @@
       <c r="G91" s="6"/>
       <c r="H91" s="7"/>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A92" s="4"/>
       <c r="B92" s="5"/>
       <c r="C92" s="42"/>
@@ -7084,7 +7070,7 @@
       <c r="G92" s="6"/>
       <c r="H92" s="7"/>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A93" s="4"/>
       <c r="B93" s="5"/>
       <c r="C93" s="42"/>
@@ -7094,7 +7080,7 @@
       <c r="G93" s="6"/>
       <c r="H93" s="7"/>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A94" s="4"/>
       <c r="B94" s="5"/>
       <c r="C94" s="42"/>
@@ -7104,7 +7090,7 @@
       <c r="G94" s="6"/>
       <c r="H94" s="7"/>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A95" s="4"/>
       <c r="B95" s="5"/>
       <c r="C95" s="42"/>
@@ -7114,7 +7100,7 @@
       <c r="G95" s="6"/>
       <c r="H95" s="7"/>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A96" s="4"/>
       <c r="B96" s="5"/>
       <c r="C96" s="42"/>
@@ -7124,7 +7110,7 @@
       <c r="G96" s="6"/>
       <c r="H96" s="7"/>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A97" s="4"/>
       <c r="B97" s="5"/>
       <c r="C97" s="42"/>
@@ -7134,7 +7120,7 @@
       <c r="G97" s="6"/>
       <c r="H97" s="7"/>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A98" s="4"/>
       <c r="B98" s="5"/>
       <c r="C98" s="42"/>
@@ -7144,7 +7130,7 @@
       <c r="G98" s="6"/>
       <c r="H98" s="7"/>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A99" s="4"/>
       <c r="B99" s="5"/>
       <c r="C99" s="42"/>
@@ -7154,7 +7140,7 @@
       <c r="G99" s="6"/>
       <c r="H99" s="7"/>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A100" s="4"/>
       <c r="B100" s="5"/>
       <c r="C100" s="42"/>
@@ -7164,7 +7150,7 @@
       <c r="G100" s="6"/>
       <c r="H100" s="7"/>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A101" s="4"/>
       <c r="B101" s="5"/>
       <c r="C101" s="42"/>
@@ -7174,7 +7160,7 @@
       <c r="G101" s="6"/>
       <c r="H101" s="7"/>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A102" s="4"/>
       <c r="B102" s="5"/>
       <c r="C102" s="42"/>
@@ -7184,7 +7170,7 @@
       <c r="G102" s="6"/>
       <c r="H102" s="7"/>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A103" s="4"/>
       <c r="B103" s="5"/>
       <c r="C103" s="42"/>
@@ -7194,7 +7180,7 @@
       <c r="G103" s="6"/>
       <c r="H103" s="7"/>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A104" s="4"/>
       <c r="B104" s="5"/>
       <c r="C104" s="42"/>
@@ -7204,7 +7190,7 @@
       <c r="G104" s="6"/>
       <c r="H104" s="7"/>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A105" s="4"/>
       <c r="B105" s="5"/>
       <c r="C105" s="42"/>
@@ -7214,7 +7200,7 @@
       <c r="G105" s="6"/>
       <c r="H105" s="7"/>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A106" s="4"/>
       <c r="B106" s="5"/>
       <c r="C106" s="42"/>
@@ -7224,7 +7210,7 @@
       <c r="G106" s="6"/>
       <c r="H106" s="7"/>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A107" s="4"/>
       <c r="B107" s="5"/>
       <c r="C107" s="42"/>
@@ -7234,7 +7220,7 @@
       <c r="G107" s="6"/>
       <c r="H107" s="7"/>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A108" s="4"/>
       <c r="B108" s="5"/>
       <c r="C108" s="42"/>
@@ -7244,7 +7230,7 @@
       <c r="G108" s="6"/>
       <c r="H108" s="7"/>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A109" s="4"/>
       <c r="B109" s="5"/>
       <c r="C109" s="42"/>
@@ -7254,7 +7240,7 @@
       <c r="G109" s="6"/>
       <c r="H109" s="7"/>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A110" s="4"/>
       <c r="B110" s="5"/>
       <c r="C110" s="42"/>
@@ -7264,7 +7250,7 @@
       <c r="G110" s="6"/>
       <c r="H110" s="7"/>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A111" s="4"/>
       <c r="B111" s="5"/>
       <c r="C111" s="42"/>
@@ -7274,7 +7260,7 @@
       <c r="G111" s="6"/>
       <c r="H111" s="7"/>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A112" s="4"/>
       <c r="B112" s="5"/>
       <c r="C112" s="42"/>
@@ -7284,7 +7270,7 @@
       <c r="G112" s="6"/>
       <c r="H112" s="7"/>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A113" s="4"/>
       <c r="B113" s="5"/>
       <c r="C113" s="42"/>
@@ -7294,7 +7280,7 @@
       <c r="G113" s="6"/>
       <c r="H113" s="7"/>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A114" s="4"/>
       <c r="B114" s="5"/>
       <c r="C114" s="42"/>
@@ -7304,7 +7290,7 @@
       <c r="G114" s="6"/>
       <c r="H114" s="7"/>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A115" s="4"/>
       <c r="B115" s="5"/>
       <c r="C115" s="42"/>
@@ -7314,7 +7300,7 @@
       <c r="G115" s="6"/>
       <c r="H115" s="7"/>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A116" s="4"/>
       <c r="B116" s="5"/>
       <c r="C116" s="42"/>
@@ -7324,7 +7310,7 @@
       <c r="G116" s="6"/>
       <c r="H116" s="7"/>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A117" s="4"/>
       <c r="B117" s="5"/>
       <c r="C117" s="42"/>
@@ -7334,7 +7320,7 @@
       <c r="G117" s="6"/>
       <c r="H117" s="7"/>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A118" s="4"/>
       <c r="B118" s="5"/>
       <c r="C118" s="42"/>
@@ -7344,7 +7330,7 @@
       <c r="G118" s="6"/>
       <c r="H118" s="7"/>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A119" s="4"/>
       <c r="B119" s="5"/>
       <c r="C119" s="42"/>
@@ -7354,7 +7340,7 @@
       <c r="G119" s="6"/>
       <c r="H119" s="7"/>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A120" s="4"/>
       <c r="B120" s="5"/>
       <c r="C120" s="42"/>
@@ -7364,7 +7350,7 @@
       <c r="G120" s="6"/>
       <c r="H120" s="7"/>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A121" s="4"/>
       <c r="B121" s="5"/>
       <c r="C121" s="42"/>
@@ -7374,7 +7360,7 @@
       <c r="G121" s="6"/>
       <c r="H121" s="7"/>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A122" s="4"/>
       <c r="B122" s="5"/>
       <c r="C122" s="42"/>
@@ -7384,7 +7370,7 @@
       <c r="G122" s="6"/>
       <c r="H122" s="7"/>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A123" s="4"/>
       <c r="B123" s="5"/>
       <c r="C123" s="42"/>
@@ -7394,7 +7380,7 @@
       <c r="G123" s="6"/>
       <c r="H123" s="7"/>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A124" s="4"/>
       <c r="B124" s="5"/>
       <c r="C124" s="42"/>
@@ -7404,7 +7390,7 @@
       <c r="G124" s="6"/>
       <c r="H124" s="7"/>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A125" s="4"/>
       <c r="B125" s="5"/>
       <c r="C125" s="42"/>
@@ -7414,7 +7400,7 @@
       <c r="G125" s="6"/>
       <c r="H125" s="7"/>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A126" s="4"/>
       <c r="B126" s="5"/>
       <c r="C126" s="42"/>
@@ -7424,7 +7410,7 @@
       <c r="G126" s="6"/>
       <c r="H126" s="7"/>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A127" s="4"/>
       <c r="B127" s="5"/>
       <c r="C127" s="42"/>
@@ -7434,7 +7420,7 @@
       <c r="G127" s="6"/>
       <c r="H127" s="7"/>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A128" s="4"/>
       <c r="B128" s="5"/>
       <c r="C128" s="42"/>
@@ -7444,7 +7430,7 @@
       <c r="G128" s="6"/>
       <c r="H128" s="7"/>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A129" s="4"/>
       <c r="B129" s="5"/>
       <c r="C129" s="42"/>
@@ -7454,7 +7440,7 @@
       <c r="G129" s="6"/>
       <c r="H129" s="7"/>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A130" s="4"/>
       <c r="B130" s="5"/>
       <c r="C130" s="42"/>
@@ -7464,7 +7450,7 @@
       <c r="G130" s="6"/>
       <c r="H130" s="7"/>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A131" s="4"/>
       <c r="B131" s="5"/>
       <c r="C131" s="42"/>
@@ -7474,7 +7460,7 @@
       <c r="G131" s="6"/>
       <c r="H131" s="7"/>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A132" s="4"/>
       <c r="B132" s="5"/>
       <c r="C132" s="42"/>
@@ -7484,7 +7470,7 @@
       <c r="G132" s="6"/>
       <c r="H132" s="7"/>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A133" s="4"/>
       <c r="B133" s="5"/>
       <c r="C133" s="42"/>
@@ -7494,7 +7480,7 @@
       <c r="G133" s="6"/>
       <c r="H133" s="7"/>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A134" s="4"/>
       <c r="B134" s="5"/>
       <c r="C134" s="42"/>
@@ -7504,7 +7490,7 @@
       <c r="G134" s="6"/>
       <c r="H134" s="7"/>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A135" s="4"/>
       <c r="B135" s="5"/>
       <c r="C135" s="42"/>
@@ -7514,7 +7500,7 @@
       <c r="G135" s="6"/>
       <c r="H135" s="7"/>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A136" s="4"/>
       <c r="B136" s="5"/>
       <c r="C136" s="42"/>
@@ -7524,7 +7510,7 @@
       <c r="G136" s="6"/>
       <c r="H136" s="7"/>
     </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A137" s="4"/>
       <c r="B137" s="5"/>
       <c r="C137" s="42"/>
@@ -7534,7 +7520,7 @@
       <c r="G137" s="6"/>
       <c r="H137" s="7"/>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A138" s="4"/>
       <c r="B138" s="5"/>
       <c r="C138" s="42"/>
@@ -7544,7 +7530,7 @@
       <c r="G138" s="6"/>
       <c r="H138" s="7"/>
     </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A139" s="4"/>
       <c r="B139" s="5"/>
       <c r="C139" s="42"/>
@@ -7554,7 +7540,7 @@
       <c r="G139" s="6"/>
       <c r="H139" s="7"/>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A140" s="4"/>
       <c r="B140" s="5"/>
       <c r="C140" s="42"/>
@@ -7564,7 +7550,7 @@
       <c r="G140" s="6"/>
       <c r="H140" s="7"/>
     </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A141" s="4"/>
       <c r="B141" s="5"/>
       <c r="C141" s="42"/>
@@ -7574,7 +7560,7 @@
       <c r="G141" s="6"/>
       <c r="H141" s="7"/>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A142" s="4"/>
       <c r="B142" s="5"/>
       <c r="C142" s="42"/>
@@ -7584,7 +7570,7 @@
       <c r="G142" s="6"/>
       <c r="H142" s="7"/>
     </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A143" s="4"/>
       <c r="B143" s="5"/>
       <c r="C143" s="42"/>
@@ -7594,7 +7580,7 @@
       <c r="G143" s="6"/>
       <c r="H143" s="7"/>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A144" s="4"/>
       <c r="B144" s="5"/>
       <c r="C144" s="42"/>
@@ -7604,7 +7590,7 @@
       <c r="G144" s="6"/>
       <c r="H144" s="7"/>
     </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A145" s="4"/>
       <c r="B145" s="5"/>
       <c r="C145" s="42"/>
@@ -7614,7 +7600,7 @@
       <c r="G145" s="6"/>
       <c r="H145" s="7"/>
     </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A146" s="4"/>
       <c r="B146" s="5"/>
       <c r="C146" s="42"/>
@@ -7624,7 +7610,7 @@
       <c r="G146" s="6"/>
       <c r="H146" s="7"/>
     </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A147" s="4"/>
       <c r="B147" s="5"/>
       <c r="C147" s="42"/>
@@ -7634,7 +7620,7 @@
       <c r="G147" s="6"/>
       <c r="H147" s="7"/>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A148" s="4"/>
       <c r="B148" s="5"/>
       <c r="C148" s="42"/>
@@ -7644,7 +7630,7 @@
       <c r="G148" s="6"/>
       <c r="H148" s="7"/>
     </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A149" s="4"/>
       <c r="B149" s="5"/>
       <c r="C149" s="42"/>
@@ -7654,7 +7640,7 @@
       <c r="G149" s="6"/>
       <c r="H149" s="7"/>
     </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A150" s="4"/>
       <c r="B150" s="5"/>
       <c r="C150" s="42"/>
@@ -7664,7 +7650,7 @@
       <c r="G150" s="6"/>
       <c r="H150" s="7"/>
     </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A151" s="4"/>
       <c r="B151" s="5"/>
       <c r="C151" s="42"/>
@@ -7674,7 +7660,7 @@
       <c r="G151" s="6"/>
       <c r="H151" s="7"/>
     </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A152" s="4"/>
       <c r="B152" s="5"/>
       <c r="C152" s="42"/>
@@ -7684,7 +7670,7 @@
       <c r="G152" s="6"/>
       <c r="H152" s="7"/>
     </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A153" s="4"/>
       <c r="B153" s="5"/>
       <c r="C153" s="42"/>
@@ -7694,7 +7680,7 @@
       <c r="G153" s="6"/>
       <c r="H153" s="7"/>
     </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A154" s="4"/>
       <c r="B154" s="5"/>
       <c r="C154" s="42"/>
@@ -7704,7 +7690,7 @@
       <c r="G154" s="6"/>
       <c r="H154" s="7"/>
     </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A155" s="4"/>
       <c r="B155" s="5"/>
       <c r="C155" s="42"/>
@@ -7714,7 +7700,7 @@
       <c r="G155" s="6"/>
       <c r="H155" s="7"/>
     </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A156" s="4"/>
       <c r="B156" s="5"/>
       <c r="C156" s="42"/>
@@ -7724,7 +7710,7 @@
       <c r="G156" s="6"/>
       <c r="H156" s="7"/>
     </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A157" s="4"/>
       <c r="B157" s="5"/>
       <c r="C157" s="42"/>
@@ -7734,7 +7720,7 @@
       <c r="G157" s="6"/>
       <c r="H157" s="7"/>
     </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A158" s="4"/>
       <c r="B158" s="5"/>
       <c r="C158" s="42"/>
@@ -7744,7 +7730,7 @@
       <c r="G158" s="6"/>
       <c r="H158" s="7"/>
     </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A159" s="4"/>
       <c r="B159" s="5"/>
       <c r="C159" s="42"/>
@@ -7754,7 +7740,7 @@
       <c r="G159" s="6"/>
       <c r="H159" s="7"/>
     </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A160" s="4"/>
       <c r="B160" s="5"/>
       <c r="C160" s="42"/>
@@ -7764,7 +7750,7 @@
       <c r="G160" s="6"/>
       <c r="H160" s="7"/>
     </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A161" s="4"/>
       <c r="B161" s="5"/>
       <c r="C161" s="42"/>
@@ -7774,7 +7760,7 @@
       <c r="G161" s="6"/>
       <c r="H161" s="7"/>
     </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A162" s="4"/>
       <c r="B162" s="5"/>
       <c r="C162" s="42"/>
@@ -7784,7 +7770,7 @@
       <c r="G162" s="6"/>
       <c r="H162" s="7"/>
     </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A163" s="4"/>
       <c r="B163" s="5"/>
       <c r="C163" s="42"/>
@@ -7794,7 +7780,7 @@
       <c r="G163" s="6"/>
       <c r="H163" s="7"/>
     </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A164" s="4"/>
       <c r="B164" s="5"/>
       <c r="C164" s="42"/>
@@ -7804,7 +7790,7 @@
       <c r="G164" s="6"/>
       <c r="H164" s="7"/>
     </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A165" s="4"/>
       <c r="B165" s="5"/>
       <c r="C165" s="42"/>
@@ -7814,7 +7800,7 @@
       <c r="G165" s="6"/>
       <c r="H165" s="7"/>
     </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A166" s="4"/>
       <c r="B166" s="5"/>
       <c r="C166" s="42"/>
@@ -7824,7 +7810,7 @@
       <c r="G166" s="6"/>
       <c r="H166" s="7"/>
     </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A167" s="4"/>
       <c r="B167" s="5"/>
       <c r="C167" s="42"/>
@@ -7834,7 +7820,7 @@
       <c r="G167" s="6"/>
       <c r="H167" s="7"/>
     </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A168" s="4"/>
       <c r="B168" s="5"/>
       <c r="C168" s="42"/>
@@ -7844,7 +7830,7 @@
       <c r="G168" s="6"/>
       <c r="H168" s="7"/>
     </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A169" s="4"/>
       <c r="B169" s="5"/>
       <c r="C169" s="42"/>
@@ -7854,7 +7840,7 @@
       <c r="G169" s="6"/>
       <c r="H169" s="7"/>
     </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A170" s="4"/>
       <c r="B170" s="5"/>
       <c r="C170" s="42"/>
@@ -7864,7 +7850,7 @@
       <c r="G170" s="6"/>
       <c r="H170" s="7"/>
     </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A171" s="4"/>
       <c r="B171" s="5"/>
       <c r="C171" s="42"/>
@@ -7874,7 +7860,7 @@
       <c r="G171" s="6"/>
       <c r="H171" s="7"/>
     </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A172" s="4"/>
       <c r="B172" s="5"/>
       <c r="C172" s="42"/>
@@ -7884,7 +7870,7 @@
       <c r="G172" s="6"/>
       <c r="H172" s="7"/>
     </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A173" s="4"/>
       <c r="B173" s="5"/>
       <c r="C173" s="42"/>
@@ -7894,7 +7880,7 @@
       <c r="G173" s="6"/>
       <c r="H173" s="7"/>
     </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A174" s="4"/>
       <c r="B174" s="5"/>
       <c r="C174" s="42"/>
@@ -7904,7 +7890,7 @@
       <c r="G174" s="6"/>
       <c r="H174" s="7"/>
     </row>
-    <row r="175" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A175" s="4"/>
       <c r="B175" s="5"/>
       <c r="C175" s="42"/>
@@ -7914,7 +7900,7 @@
       <c r="G175" s="6"/>
       <c r="H175" s="7"/>
     </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A176" s="4"/>
       <c r="B176" s="5"/>
       <c r="C176" s="42"/>
@@ -7924,7 +7910,7 @@
       <c r="G176" s="6"/>
       <c r="H176" s="7"/>
     </row>
-    <row r="177" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A177" s="4"/>
       <c r="B177" s="5"/>
       <c r="C177" s="42"/>
@@ -7934,7 +7920,7 @@
       <c r="G177" s="6"/>
       <c r="H177" s="7"/>
     </row>
-    <row r="178" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A178" s="4"/>
       <c r="B178" s="5"/>
       <c r="C178" s="42"/>
@@ -7944,7 +7930,7 @@
       <c r="G178" s="6"/>
       <c r="H178" s="7"/>
     </row>
-    <row r="179" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A179" s="4"/>
       <c r="B179" s="5"/>
       <c r="C179" s="42"/>
@@ -7954,7 +7940,7 @@
       <c r="G179" s="6"/>
       <c r="H179" s="7"/>
     </row>
-    <row r="180" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A180" s="4"/>
       <c r="B180" s="5"/>
       <c r="C180" s="42"/>
@@ -7964,7 +7950,7 @@
       <c r="G180" s="6"/>
       <c r="H180" s="7"/>
     </row>
-    <row r="181" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A181" s="4"/>
       <c r="B181" s="5"/>
       <c r="C181" s="42"/>
@@ -7974,7 +7960,7 @@
       <c r="G181" s="6"/>
       <c r="H181" s="7"/>
     </row>
-    <row r="182" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A182" s="4"/>
       <c r="B182" s="5"/>
       <c r="C182" s="42"/>
@@ -7984,7 +7970,7 @@
       <c r="G182" s="6"/>
       <c r="H182" s="7"/>
     </row>
-    <row r="183" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A183" s="4"/>
       <c r="B183" s="5"/>
       <c r="C183" s="42"/>
@@ -7994,7 +7980,7 @@
       <c r="G183" s="6"/>
       <c r="H183" s="7"/>
     </row>
-    <row r="184" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A184" s="4"/>
       <c r="B184" s="5"/>
       <c r="C184" s="42"/>
@@ -8004,7 +7990,7 @@
       <c r="G184" s="6"/>
       <c r="H184" s="7"/>
     </row>
-    <row r="185" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A185" s="4"/>
       <c r="B185" s="5"/>
       <c r="C185" s="42"/>
@@ -8014,7 +8000,7 @@
       <c r="G185" s="6"/>
       <c r="H185" s="7"/>
     </row>
-    <row r="186" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A186" s="4"/>
       <c r="B186" s="5"/>
       <c r="C186" s="42"/>
@@ -8024,7 +8010,7 @@
       <c r="G186" s="6"/>
       <c r="H186" s="7"/>
     </row>
-    <row r="187" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A187" s="4"/>
       <c r="B187" s="5"/>
       <c r="C187" s="42"/>
@@ -8034,7 +8020,7 @@
       <c r="G187" s="6"/>
       <c r="H187" s="7"/>
     </row>
-    <row r="188" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A188" s="4"/>
       <c r="B188" s="5"/>
       <c r="C188" s="42"/>
@@ -8044,7 +8030,7 @@
       <c r="G188" s="6"/>
       <c r="H188" s="7"/>
     </row>
-    <row r="189" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A189" s="4"/>
       <c r="B189" s="5"/>
       <c r="C189" s="42"/>
@@ -8054,7 +8040,7 @@
       <c r="G189" s="6"/>
       <c r="H189" s="7"/>
     </row>
-    <row r="190" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A190" s="4"/>
       <c r="B190" s="5"/>
       <c r="C190" s="42"/>
@@ -8064,7 +8050,7 @@
       <c r="G190" s="6"/>
       <c r="H190" s="7"/>
     </row>
-    <row r="191" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A191" s="4"/>
       <c r="B191" s="5"/>
       <c r="C191" s="42"/>
@@ -8074,7 +8060,7 @@
       <c r="G191" s="6"/>
       <c r="H191" s="7"/>
     </row>
-    <row r="192" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A192" s="4"/>
       <c r="B192" s="5"/>
       <c r="C192" s="42"/>
@@ -8084,7 +8070,7 @@
       <c r="G192" s="6"/>
       <c r="H192" s="7"/>
     </row>
-    <row r="193" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A193" s="4"/>
       <c r="B193" s="5"/>
       <c r="C193" s="42"/>
@@ -8094,7 +8080,7 @@
       <c r="G193" s="6"/>
       <c r="H193" s="7"/>
     </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A194" s="4"/>
       <c r="B194" s="5"/>
       <c r="C194" s="42"/>
@@ -8104,7 +8090,7 @@
       <c r="G194" s="6"/>
       <c r="H194" s="7"/>
     </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A195" s="4"/>
       <c r="B195" s="5"/>
       <c r="C195" s="42"/>
@@ -8114,7 +8100,7 @@
       <c r="G195" s="6"/>
       <c r="H195" s="7"/>
     </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A196" s="4"/>
       <c r="B196" s="5"/>
       <c r="C196" s="42"/>
@@ -8124,7 +8110,7 @@
       <c r="G196" s="6"/>
       <c r="H196" s="7"/>
     </row>
-    <row r="197" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A197" s="4"/>
       <c r="B197" s="5"/>
       <c r="C197" s="42"/>
@@ -8134,7 +8120,7 @@
       <c r="G197" s="6"/>
       <c r="H197" s="7"/>
     </row>
-    <row r="198" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A198" s="4"/>
       <c r="B198" s="5"/>
       <c r="C198" s="42"/>
@@ -8144,7 +8130,7 @@
       <c r="G198" s="6"/>
       <c r="H198" s="7"/>
     </row>
-    <row r="199" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A199" s="4"/>
       <c r="B199" s="5"/>
       <c r="C199" s="42"/>
@@ -8154,7 +8140,7 @@
       <c r="G199" s="6"/>
       <c r="H199" s="7"/>
     </row>
-    <row r="200" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A200" s="4"/>
       <c r="B200" s="5"/>
       <c r="C200" s="42"/>
@@ -8164,7 +8150,7 @@
       <c r="G200" s="6"/>
       <c r="H200" s="7"/>
     </row>
-    <row r="201" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A201" s="4"/>
       <c r="B201" s="5"/>
       <c r="C201" s="42"/>
@@ -8174,7 +8160,7 @@
       <c r="G201" s="6"/>
       <c r="H201" s="7"/>
     </row>
-    <row r="202" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A202" s="4"/>
       <c r="B202" s="5"/>
       <c r="C202" s="42"/>
@@ -8184,7 +8170,7 @@
       <c r="G202" s="6"/>
       <c r="H202" s="7"/>
     </row>
-    <row r="203" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A203" s="4"/>
       <c r="B203" s="5"/>
       <c r="C203" s="42"/>
@@ -8194,7 +8180,7 @@
       <c r="G203" s="6"/>
       <c r="H203" s="7"/>
     </row>
-    <row r="204" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A204" s="4"/>
       <c r="B204" s="5"/>
       <c r="C204" s="42"/>
@@ -8204,7 +8190,7 @@
       <c r="G204" s="6"/>
       <c r="H204" s="7"/>
     </row>
-    <row r="205" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A205" s="4"/>
       <c r="B205" s="5"/>
       <c r="C205" s="42"/>
@@ -8214,7 +8200,7 @@
       <c r="G205" s="6"/>
       <c r="H205" s="7"/>
     </row>
-    <row r="206" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A206" s="4"/>
       <c r="B206" s="5"/>
       <c r="C206" s="42"/>
@@ -8224,7 +8210,7 @@
       <c r="G206" s="6"/>
       <c r="H206" s="7"/>
     </row>
-    <row r="207" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A207" s="4"/>
       <c r="B207" s="5"/>
       <c r="C207" s="42"/>
@@ -8234,7 +8220,7 @@
       <c r="G207" s="6"/>
       <c r="H207" s="7"/>
     </row>
-    <row r="208" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A208" s="4"/>
       <c r="B208" s="5"/>
       <c r="C208" s="42"/>
@@ -8244,7 +8230,7 @@
       <c r="G208" s="6"/>
       <c r="H208" s="7"/>
     </row>
-    <row r="209" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A209" s="4"/>
       <c r="B209" s="5"/>
       <c r="C209" s="42"/>
@@ -8254,7 +8240,7 @@
       <c r="G209" s="6"/>
       <c r="H209" s="7"/>
     </row>
-    <row r="210" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A210" s="4"/>
       <c r="B210" s="5"/>
       <c r="C210" s="42"/>
@@ -8264,7 +8250,7 @@
       <c r="G210" s="6"/>
       <c r="H210" s="7"/>
     </row>
-    <row r="211" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A211" s="4"/>
       <c r="B211" s="5"/>
       <c r="C211" s="42"/>
@@ -8274,7 +8260,7 @@
       <c r="G211" s="6"/>
       <c r="H211" s="7"/>
     </row>
-    <row r="212" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A212" s="4"/>
       <c r="B212" s="5"/>
       <c r="C212" s="42"/>
@@ -8284,7 +8270,7 @@
       <c r="G212" s="6"/>
       <c r="H212" s="7"/>
     </row>
-    <row r="213" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A213" s="4"/>
       <c r="B213" s="5"/>
       <c r="C213" s="42"/>
@@ -8294,7 +8280,7 @@
       <c r="G213" s="6"/>
       <c r="H213" s="7"/>
     </row>
-    <row r="214" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A214" s="4"/>
       <c r="B214" s="5"/>
       <c r="C214" s="42"/>
@@ -8304,7 +8290,7 @@
       <c r="G214" s="6"/>
       <c r="H214" s="7"/>
     </row>
-    <row r="215" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A215" s="4"/>
       <c r="B215" s="5"/>
       <c r="C215" s="42"/>
@@ -8314,7 +8300,7 @@
       <c r="G215" s="6"/>
       <c r="H215" s="7"/>
     </row>
-    <row r="216" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A216" s="4"/>
       <c r="B216" s="5"/>
       <c r="C216" s="42"/>
@@ -8324,7 +8310,7 @@
       <c r="G216" s="6"/>
       <c r="H216" s="7"/>
     </row>
-    <row r="217" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A217" s="4"/>
       <c r="B217" s="5"/>
       <c r="C217" s="42"/>
@@ -8334,7 +8320,7 @@
       <c r="G217" s="6"/>
       <c r="H217" s="7"/>
     </row>
-    <row r="218" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A218" s="4"/>
       <c r="B218" s="5"/>
       <c r="C218" s="42"/>
@@ -8344,7 +8330,7 @@
       <c r="G218" s="6"/>
       <c r="H218" s="7"/>
     </row>
-    <row r="219" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A219" s="4"/>
       <c r="B219" s="5"/>
       <c r="C219" s="42"/>
@@ -8354,7 +8340,7 @@
       <c r="G219" s="6"/>
       <c r="H219" s="7"/>
     </row>
-    <row r="220" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A220" s="4"/>
       <c r="B220" s="5"/>
       <c r="C220" s="42"/>
@@ -8364,7 +8350,7 @@
       <c r="G220" s="6"/>
       <c r="H220" s="7"/>
     </row>
-    <row r="221" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A221" s="4"/>
       <c r="B221" s="5"/>
       <c r="C221" s="42"/>
@@ -8374,7 +8360,7 @@
       <c r="G221" s="6"/>
       <c r="H221" s="7"/>
     </row>
-    <row r="222" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A222" s="4"/>
       <c r="B222" s="5"/>
       <c r="C222" s="42"/>
@@ -8384,7 +8370,7 @@
       <c r="G222" s="6"/>
       <c r="H222" s="7"/>
     </row>
-    <row r="223" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A223" s="4"/>
       <c r="B223" s="5"/>
       <c r="C223" s="42"/>
@@ -8394,7 +8380,7 @@
       <c r="G223" s="6"/>
       <c r="H223" s="7"/>
     </row>
-    <row r="224" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A224" s="4"/>
       <c r="B224" s="5"/>
       <c r="C224" s="42"/>
@@ -8404,7 +8390,7 @@
       <c r="G224" s="6"/>
       <c r="H224" s="7"/>
     </row>
-    <row r="225" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A225" s="4"/>
       <c r="B225" s="5"/>
       <c r="C225" s="42"/>
@@ -8414,7 +8400,7 @@
       <c r="G225" s="6"/>
       <c r="H225" s="7"/>
     </row>
-    <row r="226" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A226" s="4"/>
       <c r="B226" s="5"/>
       <c r="C226" s="42"/>
@@ -8424,7 +8410,7 @@
       <c r="G226" s="6"/>
       <c r="H226" s="7"/>
     </row>
-    <row r="227" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A227" s="4"/>
       <c r="B227" s="5"/>
       <c r="C227" s="42"/>
@@ -8434,7 +8420,7 @@
       <c r="G227" s="6"/>
       <c r="H227" s="7"/>
     </row>
-    <row r="228" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A228" s="4"/>
       <c r="B228" s="5"/>
       <c r="C228" s="42"/>
@@ -8444,7 +8430,7 @@
       <c r="G228" s="6"/>
       <c r="H228" s="7"/>
     </row>
-    <row r="229" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A229" s="4"/>
       <c r="B229" s="5"/>
       <c r="C229" s="42"/>
@@ -8454,7 +8440,7 @@
       <c r="G229" s="6"/>
       <c r="H229" s="7"/>
     </row>
-    <row r="230" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A230" s="4"/>
       <c r="B230" s="5"/>
       <c r="C230" s="42"/>
@@ -8464,7 +8450,7 @@
       <c r="G230" s="6"/>
       <c r="H230" s="7"/>
     </row>
-    <row r="231" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A231" s="4"/>
       <c r="B231" s="5"/>
       <c r="C231" s="42"/>
@@ -8474,7 +8460,7 @@
       <c r="G231" s="6"/>
       <c r="H231" s="7"/>
     </row>
-    <row r="232" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A232" s="4"/>
       <c r="B232" s="5"/>
       <c r="C232" s="42"/>
@@ -8484,7 +8470,7 @@
       <c r="G232" s="6"/>
       <c r="H232" s="7"/>
     </row>
-    <row r="233" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A233" s="4"/>
       <c r="B233" s="5"/>
       <c r="C233" s="42"/>
@@ -8494,7 +8480,7 @@
       <c r="G233" s="6"/>
       <c r="H233" s="7"/>
     </row>
-    <row r="234" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A234" s="4"/>
       <c r="B234" s="5"/>
       <c r="C234" s="42"/>
@@ -8504,7 +8490,7 @@
       <c r="G234" s="6"/>
       <c r="H234" s="7"/>
     </row>
-    <row r="235" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A235" s="4"/>
       <c r="B235" s="5"/>
       <c r="C235" s="42"/>
@@ -8514,7 +8500,7 @@
       <c r="G235" s="6"/>
       <c r="H235" s="7"/>
     </row>
-    <row r="236" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A236" s="4"/>
       <c r="B236" s="5"/>
       <c r="C236" s="42"/>
@@ -8524,7 +8510,7 @@
       <c r="G236" s="6"/>
       <c r="H236" s="7"/>
     </row>
-    <row r="237" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A237" s="4"/>
       <c r="B237" s="5"/>
       <c r="C237" s="42"/>
@@ -8534,7 +8520,7 @@
       <c r="G237" s="6"/>
       <c r="H237" s="7"/>
     </row>
-    <row r="238" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A238" s="4"/>
       <c r="B238" s="5"/>
       <c r="C238" s="42"/>
@@ -8544,7 +8530,7 @@
       <c r="G238" s="6"/>
       <c r="H238" s="7"/>
     </row>
-    <row r="239" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A239" s="4"/>
       <c r="B239" s="5"/>
       <c r="C239" s="42"/>
@@ -8554,7 +8540,7 @@
       <c r="G239" s="6"/>
       <c r="H239" s="7"/>
     </row>
-    <row r="240" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A240" s="4"/>
       <c r="B240" s="5"/>
       <c r="C240" s="42"/>
@@ -8564,7 +8550,7 @@
       <c r="G240" s="6"/>
       <c r="H240" s="7"/>
     </row>
-    <row r="241" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A241" s="4"/>
       <c r="B241" s="5"/>
       <c r="C241" s="42"/>
@@ -8574,7 +8560,7 @@
       <c r="G241" s="6"/>
       <c r="H241" s="7"/>
     </row>
-    <row r="242" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A242" s="4"/>
       <c r="B242" s="5"/>
       <c r="C242" s="42"/>
@@ -8584,7 +8570,7 @@
       <c r="G242" s="6"/>
       <c r="H242" s="7"/>
     </row>
-    <row r="243" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A243" s="4"/>
       <c r="B243" s="5"/>
       <c r="C243" s="42"/>
@@ -8594,7 +8580,7 @@
       <c r="G243" s="6"/>
       <c r="H243" s="7"/>
     </row>
-    <row r="244" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A244" s="4"/>
       <c r="B244" s="5"/>
       <c r="C244" s="42"/>
@@ -8604,7 +8590,7 @@
       <c r="G244" s="6"/>
       <c r="H244" s="7"/>
     </row>
-    <row r="245" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A245" s="4"/>
       <c r="B245" s="5"/>
       <c r="C245" s="42"/>
@@ -8614,7 +8600,7 @@
       <c r="G245" s="6"/>
       <c r="H245" s="7"/>
     </row>
-    <row r="246" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A246" s="4"/>
       <c r="B246" s="5"/>
       <c r="C246" s="42"/>
@@ -8624,7 +8610,7 @@
       <c r="G246" s="6"/>
       <c r="H246" s="7"/>
     </row>
-    <row r="247" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A247" s="4"/>
       <c r="B247" s="5"/>
       <c r="C247" s="42"/>
@@ -8634,7 +8620,7 @@
       <c r="G247" s="6"/>
       <c r="H247" s="7"/>
     </row>
-    <row r="248" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A248" s="4"/>
       <c r="B248" s="5"/>
       <c r="C248" s="42"/>
@@ -8644,7 +8630,7 @@
       <c r="G248" s="6"/>
       <c r="H248" s="7"/>
     </row>
-    <row r="249" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A249" s="4"/>
       <c r="B249" s="5"/>
       <c r="C249" s="42"/>
@@ -8654,7 +8640,7 @@
       <c r="G249" s="6"/>
       <c r="H249" s="7"/>
     </row>
-    <row r="250" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A250" s="4"/>
       <c r="B250" s="5"/>
       <c r="C250" s="42"/>
@@ -8664,7 +8650,7 @@
       <c r="G250" s="6"/>
       <c r="H250" s="7"/>
     </row>
-    <row r="251" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A251" s="4"/>
       <c r="B251" s="5"/>
       <c r="C251" s="42"/>
@@ -8674,7 +8660,7 @@
       <c r="G251" s="6"/>
       <c r="H251" s="7"/>
     </row>
-    <row r="252" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A252" s="4"/>
       <c r="B252" s="5"/>
       <c r="C252" s="42"/>
@@ -8684,7 +8670,7 @@
       <c r="G252" s="6"/>
       <c r="H252" s="7"/>
     </row>
-    <row r="253" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A253" s="4"/>
       <c r="B253" s="5"/>
       <c r="C253" s="42"/>
@@ -8694,7 +8680,7 @@
       <c r="G253" s="6"/>
       <c r="H253" s="7"/>
     </row>
-    <row r="254" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A254" s="4"/>
       <c r="B254" s="5"/>
       <c r="C254" s="42"/>
@@ -8704,7 +8690,7 @@
       <c r="G254" s="6"/>
       <c r="H254" s="7"/>
     </row>
-    <row r="255" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A255" s="4"/>
       <c r="B255" s="5"/>
       <c r="C255" s="42"/>
@@ -8714,7 +8700,7 @@
       <c r="G255" s="6"/>
       <c r="H255" s="7"/>
     </row>
-    <row r="256" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A256" s="4"/>
       <c r="B256" s="5"/>
       <c r="C256" s="42"/>
@@ -8724,7 +8710,7 @@
       <c r="G256" s="6"/>
       <c r="H256" s="7"/>
     </row>
-    <row r="257" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A257" s="4"/>
       <c r="B257" s="5"/>
       <c r="C257" s="42"/>
@@ -8734,7 +8720,7 @@
       <c r="G257" s="6"/>
       <c r="H257" s="7"/>
     </row>
-    <row r="258" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A258" s="4"/>
       <c r="B258" s="5"/>
       <c r="C258" s="42"/>
@@ -8744,7 +8730,7 @@
       <c r="G258" s="6"/>
       <c r="H258" s="7"/>
     </row>
-    <row r="259" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A259" s="4"/>
       <c r="B259" s="5"/>
       <c r="C259" s="42"/>
@@ -8754,7 +8740,7 @@
       <c r="G259" s="6"/>
       <c r="H259" s="7"/>
     </row>
-    <row r="260" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A260" s="4"/>
       <c r="B260" s="5"/>
       <c r="C260" s="42"/>
@@ -8764,7 +8750,7 @@
       <c r="G260" s="6"/>
       <c r="H260" s="7"/>
     </row>
-    <row r="261" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A261" s="4"/>
       <c r="B261" s="5"/>
       <c r="C261" s="42"/>
@@ -8774,7 +8760,7 @@
       <c r="G261" s="6"/>
       <c r="H261" s="7"/>
     </row>
-    <row r="262" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A262" s="4"/>
       <c r="B262" s="5"/>
       <c r="C262" s="42"/>
@@ -8784,7 +8770,7 @@
       <c r="G262" s="6"/>
       <c r="H262" s="7"/>
     </row>
-    <row r="263" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A263" s="4"/>
       <c r="B263" s="5"/>
       <c r="C263" s="42"/>
@@ -8794,7 +8780,7 @@
       <c r="G263" s="6"/>
       <c r="H263" s="7"/>
     </row>
-    <row r="264" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A264" s="4"/>
       <c r="B264" s="5"/>
       <c r="C264" s="42"/>
@@ -8804,7 +8790,7 @@
       <c r="G264" s="6"/>
       <c r="H264" s="7"/>
     </row>
-    <row r="265" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A265" s="4"/>
       <c r="B265" s="5"/>
       <c r="C265" s="42"/>
@@ -8814,7 +8800,7 @@
       <c r="G265" s="6"/>
       <c r="H265" s="7"/>
     </row>
-    <row r="266" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A266" s="4"/>
       <c r="B266" s="5"/>
       <c r="C266" s="42"/>
@@ -8824,7 +8810,7 @@
       <c r="G266" s="6"/>
       <c r="H266" s="7"/>
     </row>
-    <row r="267" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A267" s="4"/>
       <c r="B267" s="5"/>
       <c r="C267" s="42"/>
@@ -8834,7 +8820,7 @@
       <c r="G267" s="6"/>
       <c r="H267" s="7"/>
     </row>
-    <row r="268" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A268" s="4"/>
       <c r="B268" s="5"/>
       <c r="C268" s="42"/>
@@ -8844,7 +8830,7 @@
       <c r="G268" s="6"/>
       <c r="H268" s="7"/>
     </row>
-    <row r="269" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A269" s="4"/>
       <c r="B269" s="5"/>
       <c r="C269" s="42"/>
@@ -8854,7 +8840,7 @@
       <c r="G269" s="6"/>
       <c r="H269" s="7"/>
     </row>
-    <row r="270" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A270" s="4"/>
       <c r="B270" s="5"/>
       <c r="C270" s="42"/>
@@ -8864,7 +8850,7 @@
       <c r="G270" s="6"/>
       <c r="H270" s="7"/>
     </row>
-    <row r="271" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A271" s="4"/>
       <c r="B271" s="5"/>
       <c r="C271" s="42"/>
@@ -8874,7 +8860,7 @@
       <c r="G271" s="6"/>
       <c r="H271" s="7"/>
     </row>
-    <row r="272" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A272" s="4"/>
       <c r="B272" s="5"/>
       <c r="C272" s="42"/>
@@ -8884,7 +8870,7 @@
       <c r="G272" s="6"/>
       <c r="H272" s="7"/>
     </row>
-    <row r="273" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A273" s="4"/>
       <c r="B273" s="5"/>
       <c r="C273" s="42"/>
@@ -8894,7 +8880,7 @@
       <c r="G273" s="6"/>
       <c r="H273" s="7"/>
     </row>
-    <row r="274" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A274" s="4"/>
       <c r="B274" s="5"/>
       <c r="C274" s="42"/>
@@ -8904,7 +8890,7 @@
       <c r="G274" s="6"/>
       <c r="H274" s="7"/>
     </row>
-    <row r="275" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A275" s="4"/>
       <c r="B275" s="5"/>
       <c r="C275" s="42"/>
@@ -8914,7 +8900,7 @@
       <c r="G275" s="6"/>
       <c r="H275" s="7"/>
     </row>
-    <row r="276" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A276" s="4"/>
       <c r="B276" s="5"/>
       <c r="C276" s="42"/>
@@ -8924,7 +8910,7 @@
       <c r="G276" s="6"/>
       <c r="H276" s="7"/>
     </row>
-    <row r="277" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A277" s="4"/>
       <c r="B277" s="5"/>
       <c r="C277" s="42"/>
@@ -8934,7 +8920,7 @@
       <c r="G277" s="6"/>
       <c r="H277" s="7"/>
     </row>
-    <row r="278" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A278" s="4"/>
       <c r="B278" s="5"/>
       <c r="C278" s="42"/>
@@ -8944,7 +8930,7 @@
       <c r="G278" s="6"/>
       <c r="H278" s="7"/>
     </row>
-    <row r="279" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A279" s="4"/>
       <c r="B279" s="5"/>
       <c r="C279" s="42"/>
@@ -8954,7 +8940,7 @@
       <c r="G279" s="6"/>
       <c r="H279" s="7"/>
     </row>
-    <row r="280" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A280" s="4"/>
       <c r="B280" s="5"/>
       <c r="C280" s="42"/>
@@ -8964,7 +8950,7 @@
       <c r="G280" s="6"/>
       <c r="H280" s="7"/>
     </row>
-    <row r="281" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A281" s="4"/>
       <c r="B281" s="5"/>
       <c r="C281" s="42"/>
@@ -8974,7 +8960,7 @@
       <c r="G281" s="6"/>
       <c r="H281" s="7"/>
     </row>
-    <row r="282" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A282" s="4"/>
       <c r="B282" s="5"/>
       <c r="C282" s="42"/>
@@ -8984,7 +8970,7 @@
       <c r="G282" s="6"/>
       <c r="H282" s="7"/>
     </row>
-    <row r="283" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A283" s="4"/>
       <c r="B283" s="5"/>
       <c r="C283" s="42"/>
@@ -8994,7 +8980,7 @@
       <c r="G283" s="6"/>
       <c r="H283" s="7"/>
     </row>
-    <row r="284" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A284" s="4"/>
       <c r="B284" s="5"/>
       <c r="C284" s="42"/>
@@ -9004,7 +8990,7 @@
       <c r="G284" s="6"/>
       <c r="H284" s="7"/>
     </row>
-    <row r="285" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A285" s="4"/>
       <c r="B285" s="5"/>
       <c r="C285" s="42"/>
@@ -9014,7 +9000,7 @@
       <c r="G285" s="6"/>
       <c r="H285" s="7"/>
     </row>
-    <row r="286" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A286" s="4"/>
       <c r="B286" s="5"/>
       <c r="C286" s="42"/>
@@ -9024,7 +9010,7 @@
       <c r="G286" s="6"/>
       <c r="H286" s="7"/>
     </row>
-    <row r="287" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A287" s="4"/>
       <c r="B287" s="5"/>
       <c r="C287" s="42"/>
@@ -9034,7 +9020,7 @@
       <c r="G287" s="6"/>
       <c r="H287" s="7"/>
     </row>
-    <row r="288" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A288" s="4"/>
       <c r="B288" s="5"/>
       <c r="C288" s="42"/>
@@ -9044,7 +9030,7 @@
       <c r="G288" s="6"/>
       <c r="H288" s="7"/>
     </row>
-    <row r="289" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A289" s="4"/>
       <c r="B289" s="5"/>
       <c r="C289" s="42"/>
@@ -9054,7 +9040,7 @@
       <c r="G289" s="6"/>
       <c r="H289" s="7"/>
     </row>
-    <row r="290" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A290" s="4"/>
       <c r="B290" s="5"/>
       <c r="C290" s="42"/>
@@ -9064,7 +9050,7 @@
       <c r="G290" s="6"/>
       <c r="H290" s="7"/>
     </row>
-    <row r="291" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A291" s="4"/>
       <c r="B291" s="5"/>
       <c r="C291" s="42"/>
@@ -9074,7 +9060,7 @@
       <c r="G291" s="6"/>
       <c r="H291" s="7"/>
     </row>
-    <row r="292" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A292" s="4"/>
       <c r="B292" s="5"/>
       <c r="C292" s="42"/>
@@ -9084,7 +9070,7 @@
       <c r="G292" s="6"/>
       <c r="H292" s="7"/>
     </row>
-    <row r="293" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A293" s="4"/>
       <c r="B293" s="5"/>
       <c r="C293" s="42"/>
@@ -9094,7 +9080,7 @@
       <c r="G293" s="6"/>
       <c r="H293" s="7"/>
     </row>
-    <row r="294" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A294" s="4"/>
       <c r="B294" s="5"/>
       <c r="C294" s="42"/>
@@ -9104,7 +9090,7 @@
       <c r="G294" s="6"/>
       <c r="H294" s="7"/>
     </row>
-    <row r="295" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A295" s="4"/>
       <c r="B295" s="5"/>
       <c r="C295" s="42"/>
@@ -9114,7 +9100,7 @@
       <c r="G295" s="6"/>
       <c r="H295" s="7"/>
     </row>
-    <row r="296" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A296" s="4"/>
       <c r="B296" s="5"/>
       <c r="C296" s="42"/>
@@ -9124,7 +9110,7 @@
       <c r="G296" s="6"/>
       <c r="H296" s="7"/>
     </row>
-    <row r="297" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A297" s="4"/>
       <c r="B297" s="5"/>
       <c r="C297" s="42"/>
@@ -9134,7 +9120,7 @@
       <c r="G297" s="6"/>
       <c r="H297" s="7"/>
     </row>
-    <row r="298" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A298" s="4"/>
       <c r="B298" s="5"/>
       <c r="C298" s="42"/>
@@ -9144,7 +9130,7 @@
       <c r="G298" s="6"/>
       <c r="H298" s="7"/>
     </row>
-    <row r="299" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A299" s="4"/>
       <c r="B299" s="5"/>
       <c r="C299" s="42"/>
@@ -9154,7 +9140,7 @@
       <c r="G299" s="6"/>
       <c r="H299" s="7"/>
     </row>
-    <row r="300" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A300" s="4"/>
       <c r="B300" s="5"/>
       <c r="C300" s="42"/>
@@ -9164,7 +9150,7 @@
       <c r="G300" s="6"/>
       <c r="H300" s="7"/>
     </row>
-    <row r="301" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A301" s="4"/>
       <c r="B301" s="5"/>
       <c r="C301" s="42"/>
@@ -9174,7 +9160,7 @@
       <c r="G301" s="6"/>
       <c r="H301" s="7"/>
     </row>
-    <row r="302" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A302" s="4"/>
       <c r="B302" s="5"/>
       <c r="C302" s="42"/>
@@ -9184,7 +9170,7 @@
       <c r="G302" s="6"/>
       <c r="H302" s="7"/>
     </row>
-    <row r="303" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A303" s="4"/>
       <c r="B303" s="5"/>
       <c r="C303" s="42"/>
@@ -9194,7 +9180,7 @@
       <c r="G303" s="6"/>
       <c r="H303" s="7"/>
     </row>
-    <row r="304" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A304" s="4"/>
       <c r="B304" s="5"/>
       <c r="C304" s="42"/>
@@ -9204,7 +9190,7 @@
       <c r="G304" s="6"/>
       <c r="H304" s="7"/>
     </row>
-    <row r="305" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A305" s="4"/>
       <c r="B305" s="5"/>
       <c r="C305" s="42"/>
@@ -9214,7 +9200,7 @@
       <c r="G305" s="6"/>
       <c r="H305" s="7"/>
     </row>
-    <row r="306" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A306" s="4"/>
       <c r="B306" s="5"/>
       <c r="C306" s="42"/>
@@ -9224,7 +9210,7 @@
       <c r="G306" s="6"/>
       <c r="H306" s="7"/>
     </row>
-    <row r="307" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A307" s="4"/>
       <c r="B307" s="5"/>
       <c r="C307" s="42"/>
@@ -9234,7 +9220,7 @@
       <c r="G307" s="6"/>
       <c r="H307" s="7"/>
     </row>
-    <row r="308" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A308" s="4"/>
       <c r="B308" s="5"/>
       <c r="C308" s="42"/>
@@ -9244,7 +9230,7 @@
       <c r="G308" s="6"/>
       <c r="H308" s="7"/>
     </row>
-    <row r="309" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A309" s="4"/>
       <c r="B309" s="5"/>
       <c r="C309" s="42"/>
@@ -9254,7 +9240,7 @@
       <c r="G309" s="6"/>
       <c r="H309" s="7"/>
     </row>
-    <row r="310" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A310" s="4"/>
       <c r="B310" s="5"/>
       <c r="C310" s="42"/>
@@ -9264,7 +9250,7 @@
       <c r="G310" s="6"/>
       <c r="H310" s="7"/>
     </row>
-    <row r="311" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A311" s="4"/>
       <c r="B311" s="5"/>
       <c r="C311" s="42"/>
@@ -9274,7 +9260,7 @@
       <c r="G311" s="6"/>
       <c r="H311" s="7"/>
     </row>
-    <row r="312" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A312" s="4"/>
       <c r="B312" s="5"/>
       <c r="C312" s="42"/>
@@ -9284,7 +9270,7 @@
       <c r="G312" s="6"/>
       <c r="H312" s="7"/>
     </row>
-    <row r="313" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A313" s="4"/>
       <c r="B313" s="5"/>
       <c r="C313" s="42"/>
@@ -9294,7 +9280,7 @@
       <c r="G313" s="6"/>
       <c r="H313" s="7"/>
     </row>
-    <row r="314" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A314" s="4"/>
       <c r="B314" s="5"/>
       <c r="C314" s="42"/>
@@ -9304,7 +9290,7 @@
       <c r="G314" s="6"/>
       <c r="H314" s="7"/>
     </row>
-    <row r="315" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A315" s="4"/>
       <c r="B315" s="5"/>
       <c r="C315" s="42"/>
@@ -9314,7 +9300,7 @@
       <c r="G315" s="6"/>
       <c r="H315" s="7"/>
     </row>
-    <row r="316" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A316" s="4"/>
       <c r="B316" s="5"/>
       <c r="C316" s="42"/>
@@ -9324,7 +9310,7 @@
       <c r="G316" s="6"/>
       <c r="H316" s="7"/>
     </row>
-    <row r="317" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A317" s="4"/>
       <c r="B317" s="5"/>
       <c r="C317" s="42"/>
@@ -9334,7 +9320,7 @@
       <c r="G317" s="6"/>
       <c r="H317" s="7"/>
     </row>
-    <row r="318" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A318" s="4"/>
       <c r="B318" s="5"/>
       <c r="C318" s="42"/>
@@ -9344,7 +9330,7 @@
       <c r="G318" s="6"/>
       <c r="H318" s="7"/>
     </row>
-    <row r="319" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A319" s="4"/>
       <c r="B319" s="5"/>
       <c r="C319" s="42"/>
@@ -9354,7 +9340,7 @@
       <c r="G319" s="6"/>
       <c r="H319" s="7"/>
     </row>
-    <row r="320" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A320" s="4"/>
       <c r="B320" s="5"/>
       <c r="C320" s="42"/>
@@ -9364,7 +9350,7 @@
       <c r="G320" s="6"/>
       <c r="H320" s="7"/>
     </row>
-    <row r="321" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A321" s="4"/>
       <c r="B321" s="5"/>
       <c r="C321" s="42"/>
@@ -9374,7 +9360,7 @@
       <c r="G321" s="6"/>
       <c r="H321" s="7"/>
     </row>
-    <row r="322" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A322" s="4"/>
       <c r="B322" s="5"/>
       <c r="C322" s="42"/>
@@ -9384,7 +9370,7 @@
       <c r="G322" s="6"/>
       <c r="H322" s="7"/>
     </row>
-    <row r="323" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A323" s="4"/>
       <c r="B323" s="5"/>
       <c r="C323" s="42"/>
@@ -9394,7 +9380,7 @@
       <c r="G323" s="6"/>
       <c r="H323" s="7"/>
     </row>
-    <row r="324" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A324" s="4"/>
       <c r="B324" s="5"/>
       <c r="C324" s="42"/>
@@ -9404,7 +9390,7 @@
       <c r="G324" s="6"/>
       <c r="H324" s="7"/>
     </row>
-    <row r="325" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A325" s="4"/>
       <c r="B325" s="5"/>
       <c r="C325" s="42"/>
@@ -9414,7 +9400,7 @@
       <c r="G325" s="6"/>
       <c r="H325" s="7"/>
     </row>
-    <row r="326" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A326" s="4"/>
       <c r="B326" s="5"/>
       <c r="C326" s="42"/>
@@ -9424,7 +9410,7 @@
       <c r="G326" s="6"/>
       <c r="H326" s="7"/>
     </row>
-    <row r="327" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A327" s="4"/>
       <c r="B327" s="5"/>
       <c r="C327" s="42"/>
@@ -9434,7 +9420,7 @@
       <c r="G327" s="6"/>
       <c r="H327" s="7"/>
     </row>
-    <row r="328" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A328" s="4"/>
       <c r="B328" s="5"/>
       <c r="C328" s="42"/>
@@ -9444,7 +9430,7 @@
       <c r="G328" s="6"/>
       <c r="H328" s="7"/>
     </row>
-    <row r="329" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A329" s="4"/>
       <c r="B329" s="5"/>
       <c r="C329" s="42"/>
@@ -9454,7 +9440,7 @@
       <c r="G329" s="6"/>
       <c r="H329" s="7"/>
     </row>
-    <row r="330" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A330" s="4"/>
       <c r="B330" s="5"/>
       <c r="C330" s="42"/>
@@ -9464,7 +9450,7 @@
       <c r="G330" s="6"/>
       <c r="H330" s="7"/>
     </row>
-    <row r="331" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A331" s="4"/>
       <c r="B331" s="5"/>
       <c r="C331" s="42"/>
@@ -9474,7 +9460,7 @@
       <c r="G331" s="6"/>
       <c r="H331" s="7"/>
     </row>
-    <row r="332" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A332" s="4"/>
       <c r="B332" s="5"/>
       <c r="C332" s="42"/>
@@ -9484,7 +9470,7 @@
       <c r="G332" s="6"/>
       <c r="H332" s="7"/>
     </row>
-    <row r="333" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A333" s="4"/>
       <c r="B333" s="5"/>
       <c r="C333" s="42"/>
@@ -9494,7 +9480,7 @@
       <c r="G333" s="6"/>
       <c r="H333" s="7"/>
     </row>
-    <row r="334" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A334" s="4"/>
       <c r="B334" s="5"/>
       <c r="C334" s="42"/>
@@ -9504,7 +9490,7 @@
       <c r="G334" s="6"/>
       <c r="H334" s="7"/>
     </row>
-    <row r="335" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A335" s="4"/>
       <c r="B335" s="5"/>
       <c r="C335" s="42"/>
@@ -9514,7 +9500,7 @@
       <c r="G335" s="6"/>
       <c r="H335" s="7"/>
     </row>
-    <row r="336" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A336" s="4"/>
       <c r="B336" s="5"/>
       <c r="C336" s="42"/>
@@ -9524,7 +9510,7 @@
       <c r="G336" s="6"/>
       <c r="H336" s="7"/>
     </row>
-    <row r="337" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A337" s="4"/>
       <c r="B337" s="5"/>
       <c r="C337" s="42"/>
@@ -9534,7 +9520,7 @@
       <c r="G337" s="6"/>
       <c r="H337" s="7"/>
     </row>
-    <row r="338" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A338" s="4"/>
       <c r="B338" s="5"/>
       <c r="C338" s="42"/>
@@ -9544,7 +9530,7 @@
       <c r="G338" s="6"/>
       <c r="H338" s="7"/>
     </row>
-    <row r="339" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A339" s="4"/>
       <c r="B339" s="5"/>
       <c r="C339" s="42"/>
@@ -9554,7 +9540,7 @@
       <c r="G339" s="6"/>
       <c r="H339" s="7"/>
     </row>
-    <row r="340" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A340" s="4"/>
       <c r="B340" s="5"/>
       <c r="C340" s="42"/>
@@ -9564,7 +9550,7 @@
       <c r="G340" s="6"/>
       <c r="H340" s="7"/>
     </row>
-    <row r="341" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A341" s="4"/>
       <c r="B341" s="5"/>
       <c r="C341" s="42"/>
@@ -9574,7 +9560,7 @@
       <c r="G341" s="6"/>
       <c r="H341" s="7"/>
     </row>
-    <row r="342" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A342" s="4"/>
       <c r="B342" s="5"/>
       <c r="C342" s="42"/>
@@ -9584,7 +9570,7 @@
       <c r="G342" s="6"/>
       <c r="H342" s="7"/>
     </row>
-    <row r="343" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A343" s="4"/>
       <c r="B343" s="5"/>
       <c r="C343" s="42"/>
@@ -9594,7 +9580,7 @@
       <c r="G343" s="6"/>
       <c r="H343" s="7"/>
     </row>
-    <row r="344" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A344" s="4"/>
       <c r="B344" s="5"/>
       <c r="C344" s="42"/>
@@ -9604,7 +9590,7 @@
       <c r="G344" s="6"/>
       <c r="H344" s="7"/>
     </row>
-    <row r="345" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A345" s="4"/>
       <c r="B345" s="5"/>
       <c r="C345" s="42"/>
@@ -9614,7 +9600,7 @@
       <c r="G345" s="6"/>
       <c r="H345" s="7"/>
     </row>
-    <row r="346" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A346" s="4"/>
       <c r="B346" s="5"/>
       <c r="C346" s="42"/>
@@ -9624,7 +9610,7 @@
       <c r="G346" s="6"/>
       <c r="H346" s="7"/>
     </row>
-    <row r="347" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A347" s="4"/>
       <c r="B347" s="5"/>
       <c r="C347" s="42"/>
@@ -9634,7 +9620,7 @@
       <c r="G347" s="6"/>
       <c r="H347" s="7"/>
     </row>
-    <row r="348" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A348" s="4"/>
       <c r="B348" s="5"/>
       <c r="C348" s="42"/>
@@ -9644,7 +9630,7 @@
       <c r="G348" s="6"/>
       <c r="H348" s="7"/>
     </row>
-    <row r="349" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A349" s="4"/>
       <c r="B349" s="5"/>
       <c r="C349" s="42"/>
@@ -9654,7 +9640,7 @@
       <c r="G349" s="6"/>
       <c r="H349" s="7"/>
     </row>
-    <row r="350" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A350" s="4"/>
       <c r="B350" s="5"/>
       <c r="C350" s="42"/>
@@ -9664,7 +9650,7 @@
       <c r="G350" s="6"/>
       <c r="H350" s="7"/>
     </row>
-    <row r="351" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A351" s="4"/>
       <c r="B351" s="5"/>
       <c r="C351" s="42"/>
@@ -9674,7 +9660,7 @@
       <c r="G351" s="6"/>
       <c r="H351" s="7"/>
     </row>
-    <row r="352" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A352" s="4"/>
       <c r="B352" s="5"/>
       <c r="C352" s="42"/>
@@ -9684,7 +9670,7 @@
       <c r="G352" s="6"/>
       <c r="H352" s="7"/>
     </row>
-    <row r="353" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A353" s="4"/>
       <c r="B353" s="5"/>
       <c r="C353" s="42"/>
@@ -9694,7 +9680,7 @@
       <c r="G353" s="6"/>
       <c r="H353" s="7"/>
     </row>
-    <row r="354" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A354" s="4"/>
       <c r="B354" s="5"/>
       <c r="C354" s="42"/>
@@ -9704,7 +9690,7 @@
       <c r="G354" s="6"/>
       <c r="H354" s="7"/>
     </row>
-    <row r="355" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A355" s="4"/>
       <c r="B355" s="5"/>
       <c r="C355" s="42"/>
@@ -9714,7 +9700,7 @@
       <c r="G355" s="6"/>
       <c r="H355" s="7"/>
     </row>
-    <row r="356" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A356" s="4"/>
       <c r="B356" s="5"/>
       <c r="C356" s="42"/>
@@ -9724,7 +9710,7 @@
       <c r="G356" s="6"/>
       <c r="H356" s="7"/>
     </row>
-    <row r="357" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A357" s="4"/>
       <c r="B357" s="5"/>
       <c r="C357" s="42"/>
@@ -9734,7 +9720,7 @@
       <c r="G357" s="6"/>
       <c r="H357" s="7"/>
     </row>
-    <row r="358" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A358" s="4"/>
       <c r="B358" s="5"/>
       <c r="C358" s="42"/>
@@ -9744,7 +9730,7 @@
       <c r="G358" s="6"/>
       <c r="H358" s="7"/>
     </row>
-    <row r="359" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A359" s="4"/>
       <c r="B359" s="5"/>
       <c r="C359" s="42"/>
@@ -9754,7 +9740,7 @@
       <c r="G359" s="6"/>
       <c r="H359" s="7"/>
     </row>
-    <row r="360" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A360" s="4"/>
       <c r="B360" s="5"/>
       <c r="C360" s="42"/>
@@ -9764,7 +9750,7 @@
       <c r="G360" s="6"/>
       <c r="H360" s="7"/>
     </row>
-    <row r="361" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A361" s="4"/>
       <c r="B361" s="5"/>
       <c r="C361" s="42"/>
@@ -9774,7 +9760,7 @@
       <c r="G361" s="6"/>
       <c r="H361" s="7"/>
     </row>
-    <row r="362" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A362" s="4"/>
       <c r="B362" s="5"/>
       <c r="C362" s="42"/>
@@ -9784,7 +9770,7 @@
       <c r="G362" s="6"/>
       <c r="H362" s="7"/>
     </row>
-    <row r="363" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A363" s="4"/>
       <c r="B363" s="5"/>
       <c r="C363" s="42"/>
@@ -9794,7 +9780,7 @@
       <c r="G363" s="6"/>
       <c r="H363" s="7"/>
     </row>
-    <row r="364" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A364" s="4"/>
       <c r="B364" s="5"/>
       <c r="C364" s="42"/>
@@ -9804,7 +9790,7 @@
       <c r="G364" s="6"/>
       <c r="H364" s="7"/>
     </row>
-    <row r="365" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A365" s="4"/>
       <c r="B365" s="5"/>
       <c r="C365" s="42"/>
@@ -9814,7 +9800,7 @@
       <c r="G365" s="6"/>
       <c r="H365" s="7"/>
     </row>
-    <row r="366" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A366" s="4"/>
       <c r="B366" s="5"/>
       <c r="C366" s="42"/>
@@ -9824,7 +9810,7 @@
       <c r="G366" s="6"/>
       <c r="H366" s="7"/>
     </row>
-    <row r="367" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A367" s="4"/>
       <c r="B367" s="5"/>
       <c r="C367" s="42"/>
@@ -9834,7 +9820,7 @@
       <c r="G367" s="6"/>
       <c r="H367" s="7"/>
     </row>
-    <row r="368" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A368" s="4"/>
       <c r="B368" s="5"/>
       <c r="C368" s="42"/>
@@ -9844,7 +9830,7 @@
       <c r="G368" s="6"/>
       <c r="H368" s="7"/>
     </row>
-    <row r="369" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A369" s="4"/>
       <c r="B369" s="5"/>
       <c r="C369" s="42"/>
@@ -9854,7 +9840,7 @@
       <c r="G369" s="6"/>
       <c r="H369" s="7"/>
     </row>
-    <row r="370" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A370" s="4"/>
       <c r="B370" s="5"/>
       <c r="C370" s="42"/>
@@ -9864,7 +9850,7 @@
       <c r="G370" s="6"/>
       <c r="H370" s="7"/>
     </row>
-    <row r="371" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A371" s="4"/>
       <c r="B371" s="5"/>
       <c r="C371" s="42"/>
@@ -9874,7 +9860,7 @@
       <c r="G371" s="6"/>
       <c r="H371" s="7"/>
     </row>
-    <row r="372" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A372" s="4"/>
       <c r="B372" s="5"/>
       <c r="C372" s="42"/>
@@ -9884,7 +9870,7 @@
       <c r="G372" s="6"/>
       <c r="H372" s="7"/>
     </row>
-    <row r="373" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A373" s="4"/>
       <c r="B373" s="5"/>
       <c r="C373" s="42"/>
@@ -9894,7 +9880,7 @@
       <c r="G373" s="6"/>
       <c r="H373" s="7"/>
     </row>
-    <row r="374" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A374" s="4"/>
       <c r="B374" s="5"/>
       <c r="C374" s="42"/>
@@ -9904,7 +9890,7 @@
       <c r="G374" s="6"/>
       <c r="H374" s="7"/>
     </row>
-    <row r="375" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A375" s="4"/>
       <c r="B375" s="5"/>
       <c r="C375" s="42"/>
@@ -9914,7 +9900,7 @@
       <c r="G375" s="6"/>
       <c r="H375" s="7"/>
     </row>
-    <row r="376" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A376" s="4"/>
       <c r="B376" s="5"/>
       <c r="C376" s="42"/>
@@ -9924,7 +9910,7 @@
       <c r="G376" s="6"/>
       <c r="H376" s="7"/>
     </row>
-    <row r="377" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A377" s="4"/>
       <c r="B377" s="5"/>
       <c r="C377" s="42"/>
@@ -9934,7 +9920,7 @@
       <c r="G377" s="6"/>
       <c r="H377" s="7"/>
     </row>
-    <row r="378" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A378" s="4"/>
       <c r="B378" s="5"/>
       <c r="C378" s="42"/>
@@ -9944,7 +9930,7 @@
       <c r="G378" s="6"/>
       <c r="H378" s="7"/>
     </row>
-    <row r="379" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A379" s="4"/>
       <c r="B379" s="5"/>
       <c r="C379" s="42"/>
@@ -9954,7 +9940,7 @@
       <c r="G379" s="6"/>
       <c r="H379" s="7"/>
     </row>
-    <row r="380" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A380" s="4"/>
       <c r="B380" s="5"/>
       <c r="C380" s="42"/>
@@ -9964,7 +9950,7 @@
       <c r="G380" s="6"/>
       <c r="H380" s="7"/>
     </row>
-    <row r="381" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A381" s="4"/>
       <c r="B381" s="5"/>
       <c r="C381" s="42"/>
@@ -9974,7 +9960,7 @@
       <c r="G381" s="6"/>
       <c r="H381" s="7"/>
     </row>
-    <row r="382" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A382" s="4"/>
       <c r="B382" s="5"/>
       <c r="C382" s="42"/>
@@ -9984,7 +9970,7 @@
       <c r="G382" s="6"/>
       <c r="H382" s="7"/>
     </row>
-    <row r="383" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A383" s="4"/>
       <c r="B383" s="5"/>
       <c r="C383" s="42"/>
@@ -9994,7 +9980,7 @@
       <c r="G383" s="6"/>
       <c r="H383" s="7"/>
     </row>
-    <row r="384" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A384" s="4"/>
       <c r="B384" s="5"/>
       <c r="C384" s="42"/>
@@ -10004,7 +9990,7 @@
       <c r="G384" s="6"/>
       <c r="H384" s="7"/>
     </row>
-    <row r="385" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A385" s="4"/>
       <c r="B385" s="5"/>
       <c r="C385" s="42"/>
@@ -10014,7 +10000,7 @@
       <c r="G385" s="6"/>
       <c r="H385" s="7"/>
     </row>
-    <row r="386" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A386" s="4"/>
       <c r="B386" s="5"/>
       <c r="C386" s="42"/>
@@ -10024,7 +10010,7 @@
       <c r="G386" s="6"/>
       <c r="H386" s="7"/>
     </row>
-    <row r="387" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A387" s="4"/>
       <c r="B387" s="5"/>
       <c r="C387" s="42"/>
@@ -10034,7 +10020,7 @@
       <c r="G387" s="6"/>
       <c r="H387" s="7"/>
     </row>
-    <row r="388" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A388" s="4"/>
       <c r="B388" s="5"/>
       <c r="C388" s="42"/>
@@ -10044,7 +10030,7 @@
       <c r="G388" s="6"/>
       <c r="H388" s="7"/>
     </row>
-    <row r="389" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A389" s="4"/>
       <c r="B389" s="5"/>
       <c r="C389" s="42"/>
@@ -10054,7 +10040,7 @@
       <c r="G389" s="6"/>
       <c r="H389" s="7"/>
     </row>
-    <row r="390" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A390" s="4"/>
       <c r="B390" s="5"/>
       <c r="C390" s="42"/>
@@ -10064,7 +10050,7 @@
       <c r="G390" s="6"/>
       <c r="H390" s="7"/>
     </row>
-    <row r="391" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A391" s="4"/>
       <c r="B391" s="5"/>
       <c r="C391" s="42"/>
@@ -10074,7 +10060,7 @@
       <c r="G391" s="6"/>
       <c r="H391" s="7"/>
     </row>
-    <row r="392" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A392" s="4"/>
       <c r="B392" s="5"/>
       <c r="C392" s="42"/>
@@ -10084,7 +10070,7 @@
       <c r="G392" s="6"/>
       <c r="H392" s="7"/>
     </row>
-    <row r="393" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A393" s="4"/>
       <c r="B393" s="5"/>
       <c r="C393" s="42"/>
@@ -10094,7 +10080,7 @@
       <c r="G393" s="6"/>
       <c r="H393" s="7"/>
     </row>
-    <row r="394" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A394" s="4"/>
       <c r="B394" s="5"/>
       <c r="C394" s="42"/>
@@ -10104,7 +10090,7 @@
       <c r="G394" s="6"/>
       <c r="H394" s="7"/>
     </row>
-    <row r="395" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A395" s="4"/>
       <c r="B395" s="5"/>
       <c r="C395" s="42"/>
@@ -10114,7 +10100,7 @@
       <c r="G395" s="6"/>
       <c r="H395" s="7"/>
     </row>
-    <row r="396" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A396" s="4"/>
       <c r="B396" s="5"/>
       <c r="C396" s="42"/>
@@ -10124,7 +10110,7 @@
       <c r="G396" s="6"/>
       <c r="H396" s="7"/>
     </row>
-    <row r="397" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A397" s="4"/>
       <c r="B397" s="5"/>
       <c r="C397" s="42"/>
@@ -10134,7 +10120,7 @@
       <c r="G397" s="6"/>
       <c r="H397" s="7"/>
     </row>
-    <row r="398" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A398" s="4"/>
       <c r="B398" s="5"/>
       <c r="C398" s="42"/>
@@ -10144,7 +10130,7 @@
       <c r="G398" s="6"/>
       <c r="H398" s="7"/>
     </row>
-    <row r="399" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A399" s="4"/>
       <c r="B399" s="5"/>
       <c r="C399" s="42"/>
@@ -10154,7 +10140,7 @@
       <c r="G399" s="6"/>
       <c r="H399" s="7"/>
     </row>
-    <row r="400" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A400" s="4"/>
       <c r="B400" s="5"/>
       <c r="C400" s="42"/>
@@ -10164,7 +10150,7 @@
       <c r="G400" s="6"/>
       <c r="H400" s="7"/>
     </row>
-    <row r="401" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A401" s="4"/>
       <c r="B401" s="5"/>
       <c r="C401" s="42"/>
@@ -10174,7 +10160,7 @@
       <c r="G401" s="6"/>
       <c r="H401" s="7"/>
     </row>
-    <row r="402" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A402" s="4"/>
       <c r="B402" s="5"/>
       <c r="C402" s="42"/>
@@ -10184,7 +10170,7 @@
       <c r="G402" s="6"/>
       <c r="H402" s="7"/>
     </row>
-    <row r="403" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A403" s="4"/>
       <c r="B403" s="5"/>
       <c r="C403" s="42"/>
@@ -10194,7 +10180,7 @@
       <c r="G403" s="6"/>
       <c r="H403" s="7"/>
     </row>
-    <row r="404" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A404" s="4"/>
       <c r="B404" s="5"/>
       <c r="C404" s="42"/>
@@ -10204,7 +10190,7 @@
       <c r="G404" s="6"/>
       <c r="H404" s="7"/>
     </row>
-    <row r="405" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A405" s="4"/>
       <c r="B405" s="5"/>
       <c r="C405" s="42"/>
@@ -10214,7 +10200,7 @@
       <c r="G405" s="6"/>
       <c r="H405" s="7"/>
     </row>
-    <row r="406" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A406" s="4"/>
       <c r="B406" s="5"/>
       <c r="C406" s="42"/>
@@ -10224,7 +10210,7 @@
       <c r="G406" s="6"/>
       <c r="H406" s="7"/>
     </row>
-    <row r="407" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A407" s="4"/>
       <c r="B407" s="5"/>
       <c r="C407" s="42"/>
@@ -10234,7 +10220,7 @@
       <c r="G407" s="6"/>
       <c r="H407" s="7"/>
     </row>
-    <row r="408" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A408" s="4"/>
       <c r="B408" s="5"/>
       <c r="C408" s="42"/>
@@ -10244,7 +10230,7 @@
       <c r="G408" s="6"/>
       <c r="H408" s="7"/>
     </row>
-    <row r="409" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A409" s="8"/>
       <c r="B409" s="9"/>
       <c r="C409" s="10"/>
@@ -10268,17 +10254,17 @@
     <mergeCell ref="C3:D3"/>
   </mergeCells>
   <conditionalFormatting sqref="A8:B409">
-    <cfRule type="expression" dxfId="4" priority="2">
+    <cfRule type="expression" dxfId="2" priority="2">
       <formula>MOD(ROW()-1,2)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C12:D12 F12:H12 C13:H409">
-    <cfRule type="expression" dxfId="3" priority="3">
+    <cfRule type="expression" dxfId="1" priority="3">
       <formula>MOD(ROW()-1,2)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8:H11">
-    <cfRule type="expression" dxfId="2" priority="1">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>MOD(ROW()-1,2)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10311,37 +10297,37 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB313DB0-EB85-4ACA-A552-7403B286B586}">
   <dimension ref="A1:A6"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>29</v>
       </c>
@@ -10353,9 +10339,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10491,19 +10480,15 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7ACA6411-41A0-4B6C-874D-1FC05CC4B568}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{53ACD002-FFBE-4185-9DDB-0AA3A824C3C1}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -10527,9 +10512,10 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{53ACD002-FFBE-4185-9DDB-0AA3A824C3C1}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7ACA6411-41A0-4B6C-874D-1FC05CC4B568}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>